--- a/Data/Barnacle_Toxicity_Assays.xlsx
+++ b/Data/Barnacle_Toxicity_Assays.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilysidlow/Desktop/School stuff/Bonaventura/git/esidlow_bonaventura/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDB9BB1-9366-E741-B1C3-35B3937D07A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6272028-7190-EE4F-A1B9-B2E5900C36CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" xr2:uid="{004714F4-E14F-0B40-B335-9E6A14257324}"/>
+    <workbookView xWindow="20" yWindow="5280" windowWidth="30240" windowHeight="17280" activeTab="3" xr2:uid="{004714F4-E14F-0B40-B335-9E6A14257324}"/>
   </bookViews>
   <sheets>
     <sheet name="Barnalce Toxicity Assays" sheetId="1" r:id="rId1"/>
     <sheet name="Data for R" sheetId="2" r:id="rId2"/>
+    <sheet name="Particle concentrations" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="146">
   <si>
     <t>Concentration (mg/mL)</t>
   </si>
@@ -553,6 +555,30 @@
   </si>
   <si>
     <t>% of dilution 1</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiply anything by </t>
+  </si>
+  <si>
+    <t>(5750000p/mL)/(40µg/mL)</t>
+  </si>
+  <si>
+    <t>p/µg</t>
+  </si>
+  <si>
+    <t>multiply anything by</t>
+  </si>
+  <si>
+    <t>Concentration p/mL</t>
+  </si>
+  <si>
+    <t>(1150000p/mL)/(1333µg/mL)</t>
+  </si>
+  <si>
+    <t>(1300000p/mL)/(704µg/mL)</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1406,6 +1432,94 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1427,94 +1541,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17614,24 +17643,24 @@
         <v>120</v>
       </c>
       <c r="CX2" s="12"/>
-      <c r="DR2" s="103"/>
-      <c r="DS2" s="103"/>
-      <c r="DT2" s="103"/>
-      <c r="DU2" s="103"/>
-      <c r="DV2" s="103"/>
-      <c r="DW2" s="103"/>
-      <c r="DX2" s="103"/>
-      <c r="DY2" s="103"/>
-      <c r="DZ2" s="103"/>
-      <c r="EA2" s="103"/>
-      <c r="EB2" s="103"/>
-      <c r="EC2" s="103"/>
-      <c r="ED2" s="103"/>
-      <c r="EE2" s="103"/>
-      <c r="EF2" s="103"/>
-      <c r="EG2" s="103"/>
-      <c r="EH2" s="103"/>
-      <c r="EI2" s="103"/>
+      <c r="DR2" s="133"/>
+      <c r="DS2" s="133"/>
+      <c r="DT2" s="133"/>
+      <c r="DU2" s="133"/>
+      <c r="DV2" s="133"/>
+      <c r="DW2" s="133"/>
+      <c r="DX2" s="133"/>
+      <c r="DY2" s="133"/>
+      <c r="DZ2" s="133"/>
+      <c r="EA2" s="133"/>
+      <c r="EB2" s="133"/>
+      <c r="EC2" s="133"/>
+      <c r="ED2" s="133"/>
+      <c r="EE2" s="133"/>
+      <c r="EF2" s="133"/>
+      <c r="EG2" s="133"/>
+      <c r="EH2" s="133"/>
+      <c r="EI2" s="133"/>
     </row>
     <row r="3" spans="2:139" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M3" s="8"/>
@@ -17654,17 +17683,17 @@
       <c r="BS3" t="s">
         <v>86</v>
       </c>
-      <c r="DF3" s="107" t="s">
+      <c r="DF3" s="137" t="s">
         <v>126</v>
       </c>
-      <c r="DG3" s="108"/>
-      <c r="DH3" s="108"/>
-      <c r="DI3" s="108"/>
-      <c r="DJ3" s="108"/>
-      <c r="DK3" s="108"/>
-      <c r="DL3" s="108"/>
-      <c r="DM3" s="108"/>
-      <c r="DN3" s="109"/>
+      <c r="DG3" s="138"/>
+      <c r="DH3" s="138"/>
+      <c r="DI3" s="138"/>
+      <c r="DJ3" s="138"/>
+      <c r="DK3" s="138"/>
+      <c r="DL3" s="138"/>
+      <c r="DM3" s="138"/>
+      <c r="DN3" s="139"/>
       <c r="DP3" s="93"/>
       <c r="DQ3" s="99" t="s">
         <v>129</v>
@@ -17701,55 +17730,55 @@
       <c r="EI3" s="74"/>
     </row>
     <row r="4" spans="2:139" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="135"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="126"/>
       <c r="N4" s="29"/>
-      <c r="O4" s="118" t="s">
+      <c r="O4" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="119"/>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119"/>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="119"/>
-      <c r="Z4" s="119"/>
-      <c r="AA4" s="120"/>
-      <c r="AD4" s="126" t="s">
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="129"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
+      <c r="X4" s="129"/>
+      <c r="Y4" s="129"/>
+      <c r="Z4" s="129"/>
+      <c r="AA4" s="130"/>
+      <c r="AD4" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="111"/>
-      <c r="AQ4" s="111"/>
-      <c r="AR4" s="111"/>
-      <c r="AS4" s="111"/>
-      <c r="AT4" s="112"/>
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+      <c r="AI4" s="107"/>
+      <c r="AJ4" s="107"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="107"/>
+      <c r="AM4" s="107"/>
+      <c r="AN4" s="107"/>
+      <c r="AO4" s="107"/>
+      <c r="AP4" s="107"/>
+      <c r="AQ4" s="107"/>
+      <c r="AR4" s="107"/>
+      <c r="AS4" s="107"/>
+      <c r="AT4" s="108"/>
       <c r="AX4" t="s">
         <v>72</v>
       </c>
@@ -17788,14 +17817,14 @@
       <c r="DF4" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="DG4" s="104" t="s">
+      <c r="DG4" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="DH4" s="105"/>
-      <c r="DI4" s="105"/>
-      <c r="DJ4" s="105"/>
-      <c r="DK4" s="105"/>
-      <c r="DL4" s="106"/>
+      <c r="DH4" s="135"/>
+      <c r="DI4" s="135"/>
+      <c r="DJ4" s="135"/>
+      <c r="DK4" s="135"/>
+      <c r="DL4" s="136"/>
       <c r="DM4" s="90" t="s">
         <v>123</v>
       </c>
@@ -17830,85 +17859,85 @@
       <c r="B5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="123" t="s">
+      <c r="C5" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="123" t="s">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="124"/>
-      <c r="G5" s="123" t="s">
+      <c r="F5" s="119"/>
+      <c r="G5" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="125"/>
-      <c r="I5" s="130" t="s">
+      <c r="H5" s="120"/>
+      <c r="I5" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
-      <c r="M5" s="132"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="123"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q5" s="121" t="s">
+      <c r="Q5" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="122"/>
-      <c r="S5" s="123" t="s">
+      <c r="R5" s="127"/>
+      <c r="S5" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="T5" s="124"/>
-      <c r="U5" s="123" t="s">
+      <c r="T5" s="119"/>
+      <c r="U5" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="125"/>
-      <c r="W5" s="123" t="s">
+      <c r="V5" s="120"/>
+      <c r="W5" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
-      <c r="AA5" s="125"/>
+      <c r="X5" s="112"/>
+      <c r="Y5" s="112"/>
+      <c r="Z5" s="112"/>
+      <c r="AA5" s="120"/>
       <c r="AD5" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="AE5" s="121" t="s">
+      <c r="AE5" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="AF5" s="136"/>
-      <c r="AG5" s="137"/>
-      <c r="AH5" s="121" t="s">
+      <c r="AF5" s="110"/>
+      <c r="AG5" s="111"/>
+      <c r="AH5" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="AI5" s="136"/>
-      <c r="AJ5" s="137"/>
-      <c r="AK5" s="121" t="s">
+      <c r="AI5" s="110"/>
+      <c r="AJ5" s="111"/>
+      <c r="AK5" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="AL5" s="136"/>
-      <c r="AM5" s="137"/>
-      <c r="AN5" s="117" t="s">
+      <c r="AL5" s="110"/>
+      <c r="AM5" s="111"/>
+      <c r="AN5" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="AO5" s="117"/>
-      <c r="AP5" s="117"/>
-      <c r="AQ5" s="117"/>
-      <c r="AR5" s="117"/>
-      <c r="AS5" s="117"/>
-      <c r="AT5" s="138"/>
-      <c r="AX5" s="110" t="s">
+      <c r="AO5" s="112"/>
+      <c r="AP5" s="112"/>
+      <c r="AQ5" s="112"/>
+      <c r="AR5" s="112"/>
+      <c r="AS5" s="112"/>
+      <c r="AT5" s="113"/>
+      <c r="AX5" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="AY5" s="111"/>
-      <c r="AZ5" s="111"/>
-      <c r="BA5" s="111"/>
-      <c r="BB5" s="111"/>
-      <c r="BC5" s="111"/>
-      <c r="BD5" s="111"/>
-      <c r="BE5" s="112"/>
+      <c r="AY5" s="107"/>
+      <c r="AZ5" s="107"/>
+      <c r="BA5" s="107"/>
+      <c r="BB5" s="107"/>
+      <c r="BC5" s="107"/>
+      <c r="BD5" s="107"/>
+      <c r="BE5" s="108"/>
       <c r="BJ5" s="30">
         <f>8*BJ4/24</f>
         <v>14.333333333333334</v>
@@ -17916,20 +17945,20 @@
       <c r="BK5">
         <v>0.53086419753086422</v>
       </c>
-      <c r="BO5" s="110" t="s">
+      <c r="BO5" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="BP5" s="111"/>
-      <c r="BQ5" s="111"/>
-      <c r="BR5" s="111"/>
-      <c r="BS5" s="111"/>
-      <c r="BT5" s="111"/>
-      <c r="BU5" s="111"/>
-      <c r="BV5" s="111"/>
-      <c r="BW5" s="111"/>
-      <c r="BX5" s="111"/>
-      <c r="BY5" s="111"/>
-      <c r="BZ5" s="112"/>
+      <c r="BP5" s="107"/>
+      <c r="BQ5" s="107"/>
+      <c r="BR5" s="107"/>
+      <c r="BS5" s="107"/>
+      <c r="BT5" s="107"/>
+      <c r="BU5" s="107"/>
+      <c r="BV5" s="107"/>
+      <c r="BW5" s="107"/>
+      <c r="BX5" s="107"/>
+      <c r="BY5" s="107"/>
+      <c r="BZ5" s="108"/>
       <c r="CB5">
         <v>0</v>
       </c>
@@ -17955,18 +17984,18 @@
       <c r="CS5" t="s">
         <v>118</v>
       </c>
-      <c r="CW5" s="113" t="s">
+      <c r="CW5" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="CX5" s="114"/>
-      <c r="CY5" s="113" t="s">
+      <c r="CX5" s="105"/>
+      <c r="CY5" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="CZ5" s="114"/>
-      <c r="DA5" s="113" t="s">
+      <c r="CZ5" s="105"/>
+      <c r="DA5" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="DB5" s="114"/>
+      <c r="DB5" s="105"/>
       <c r="DF5" s="79">
         <v>0</v>
       </c>
@@ -18143,22 +18172,22 @@
         <v>50</v>
       </c>
       <c r="AW6" s="35"/>
-      <c r="AX6" s="113" t="s">
+      <c r="AX6" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="AY6" s="114"/>
-      <c r="AZ6" s="113" t="s">
+      <c r="AY6" s="105"/>
+      <c r="AZ6" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="BA6" s="114"/>
-      <c r="BB6" s="113" t="s">
+      <c r="BA6" s="105"/>
+      <c r="BB6" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="BC6" s="114"/>
-      <c r="BD6" s="113" t="s">
+      <c r="BC6" s="105"/>
+      <c r="BD6" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="BE6" s="114"/>
+      <c r="BE6" s="105"/>
       <c r="BJ6" s="30">
         <f>6*BJ5/18</f>
         <v>4.7777777777777777</v>
@@ -18167,30 +18196,30 @@
         <v>1.5925925925925926</v>
       </c>
       <c r="BN6" s="34"/>
-      <c r="BO6" s="115" t="s">
+      <c r="BO6" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="BP6" s="116"/>
-      <c r="BQ6" s="115" t="s">
+      <c r="BP6" s="132"/>
+      <c r="BQ6" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="BR6" s="116"/>
-      <c r="BS6" s="115" t="s">
+      <c r="BR6" s="132"/>
+      <c r="BS6" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="BT6" s="116"/>
-      <c r="BU6" s="115" t="s">
+      <c r="BT6" s="132"/>
+      <c r="BU6" s="131" t="s">
         <v>82</v>
       </c>
-      <c r="BV6" s="116"/>
-      <c r="BW6" s="115" t="s">
+      <c r="BV6" s="132"/>
+      <c r="BW6" s="131" t="s">
         <v>82</v>
       </c>
-      <c r="BX6" s="103"/>
-      <c r="BY6" s="115" t="s">
+      <c r="BX6" s="133"/>
+      <c r="BY6" s="131" t="s">
         <v>82</v>
       </c>
-      <c r="BZ6" s="116"/>
+      <c r="BZ6" s="132"/>
       <c r="CB6">
         <v>5.7240984544934169E-2</v>
       </c>
@@ -18597,7 +18626,7 @@
         <f>6.5*20*10^4</f>
         <v>1300000</v>
       </c>
-      <c r="EA7" s="139">
+      <c r="EA7" s="103">
         <v>1120000</v>
       </c>
       <c r="EC7">
@@ -18938,7 +18967,7 @@
         <f>2*20*10^4</f>
         <v>400000</v>
       </c>
-      <c r="EA8" s="139">
+      <c r="EA8" s="103">
         <v>480000</v>
       </c>
     </row>
@@ -20033,16 +20062,16 @@
         <f t="shared" si="23"/>
         <v>4.8611111111111116</v>
       </c>
-      <c r="AX12" s="110" t="s">
+      <c r="AX12" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="AY12" s="111"/>
-      <c r="AZ12" s="111"/>
-      <c r="BA12" s="111"/>
-      <c r="BB12" s="111"/>
-      <c r="BC12" s="111"/>
-      <c r="BD12" s="111"/>
-      <c r="BE12" s="112"/>
+      <c r="AY12" s="107"/>
+      <c r="AZ12" s="107"/>
+      <c r="BA12" s="107"/>
+      <c r="BB12" s="107"/>
+      <c r="BC12" s="107"/>
+      <c r="BD12" s="107"/>
+      <c r="BE12" s="108"/>
       <c r="BJ12" s="30">
         <f>8*BJ11/24</f>
         <v>1.3333333333333333</v>
@@ -20141,7 +20170,7 @@
         <f>5.75*20*10^4</f>
         <v>1150000</v>
       </c>
-      <c r="EA12" s="139">
+      <c r="EA12" s="103">
         <v>1150000</v>
       </c>
       <c r="EC12">
@@ -20319,14 +20348,14 @@
       <c r="CT13">
         <v>120</v>
       </c>
-      <c r="CW13" s="110" t="s">
+      <c r="CW13" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="CX13" s="111"/>
-      <c r="CY13" s="111"/>
-      <c r="CZ13" s="111"/>
-      <c r="DA13" s="111"/>
-      <c r="DB13" s="112"/>
+      <c r="CX13" s="107"/>
+      <c r="CY13" s="107"/>
+      <c r="CZ13" s="107"/>
+      <c r="DA13" s="107"/>
+      <c r="DB13" s="108"/>
       <c r="DF13" s="79">
         <v>43</v>
       </c>
@@ -20380,7 +20409,7 @@
         <f>2*20*10^4</f>
         <v>400000</v>
       </c>
-      <c r="EA13" s="139">
+      <c r="EA13" s="103">
         <v>400000</v>
       </c>
     </row>
@@ -20521,20 +20550,20 @@
       <c r="BK14">
         <v>0.44444444444444442</v>
       </c>
-      <c r="BO14" s="110" t="s">
+      <c r="BO14" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="BP14" s="111"/>
-      <c r="BQ14" s="111"/>
-      <c r="BR14" s="111"/>
-      <c r="BS14" s="111"/>
-      <c r="BT14" s="111"/>
-      <c r="BU14" s="111"/>
-      <c r="BV14" s="111"/>
-      <c r="BW14" s="111"/>
-      <c r="BX14" s="111"/>
-      <c r="BY14" s="111"/>
-      <c r="BZ14" s="112"/>
+      <c r="BP14" s="107"/>
+      <c r="BQ14" s="107"/>
+      <c r="BR14" s="107"/>
+      <c r="BS14" s="107"/>
+      <c r="BT14" s="107"/>
+      <c r="BU14" s="107"/>
+      <c r="BV14" s="107"/>
+      <c r="BW14" s="107"/>
+      <c r="BX14" s="107"/>
+      <c r="BY14" s="107"/>
+      <c r="BZ14" s="108"/>
       <c r="CV14" s="43" t="s">
         <v>26</v>
       </c>
@@ -21036,7 +21065,7 @@
         <f>28.75*20*(10^4)</f>
         <v>5750000</v>
       </c>
-      <c r="EA17" s="139">
+      <c r="EA17" s="103">
         <v>5750000</v>
       </c>
       <c r="EC17">
@@ -21114,17 +21143,17 @@
         <f t="shared" si="44"/>
         <v>37.288135593220339</v>
       </c>
-      <c r="DF18" s="107" t="s">
+      <c r="DF18" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="DG18" s="108"/>
-      <c r="DH18" s="108"/>
-      <c r="DI18" s="108"/>
-      <c r="DJ18" s="108"/>
-      <c r="DK18" s="108"/>
-      <c r="DL18" s="108"/>
-      <c r="DM18" s="108"/>
-      <c r="DN18" s="109"/>
+      <c r="DG18" s="138"/>
+      <c r="DH18" s="138"/>
+      <c r="DI18" s="138"/>
+      <c r="DJ18" s="138"/>
+      <c r="DK18" s="138"/>
+      <c r="DL18" s="138"/>
+      <c r="DM18" s="138"/>
+      <c r="DN18" s="139"/>
       <c r="DQ18" s="94" t="s">
         <v>126</v>
       </c>
@@ -21155,25 +21184,25 @@
         <f>10.5*20*(10^4)</f>
         <v>2100000</v>
       </c>
-      <c r="EA18" s="139">
+      <c r="EA18" s="103">
         <v>2100000</v>
       </c>
     </row>
     <row r="19" spans="2:134" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="129"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="117"/>
       <c r="P19" s="30">
         <v>2.4691358024691357E-2</v>
       </c>
@@ -21246,14 +21275,14 @@
       <c r="DF19" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="DG19" s="104" t="s">
+      <c r="DG19" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="DH19" s="105"/>
-      <c r="DI19" s="105"/>
-      <c r="DJ19" s="105"/>
-      <c r="DK19" s="105"/>
-      <c r="DL19" s="106"/>
+      <c r="DH19" s="135"/>
+      <c r="DI19" s="135"/>
+      <c r="DJ19" s="135"/>
+      <c r="DK19" s="135"/>
+      <c r="DL19" s="136"/>
       <c r="DM19" s="90" t="s">
         <v>123</v>
       </c>
@@ -21288,25 +21317,25 @@
       <c r="B20" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="124"/>
-      <c r="E20" s="123" t="s">
+      <c r="D20" s="119"/>
+      <c r="E20" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="124"/>
-      <c r="G20" s="123" t="s">
+      <c r="F20" s="119"/>
+      <c r="G20" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="125"/>
-      <c r="I20" s="130" t="s">
+      <c r="H20" s="120"/>
+      <c r="I20" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="131"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="123"/>
       <c r="P20" s="30">
         <v>7.407407407407407E-2</v>
       </c>
@@ -22939,14 +22968,14 @@
       <c r="CT31">
         <v>2.1111111111111112</v>
       </c>
-      <c r="CW31" s="110" t="s">
+      <c r="CW31" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="CX31" s="111"/>
-      <c r="CY31" s="111"/>
-      <c r="CZ31" s="111"/>
-      <c r="DA31" s="111"/>
-      <c r="DB31" s="112"/>
+      <c r="CX31" s="107"/>
+      <c r="CY31" s="107"/>
+      <c r="CZ31" s="107"/>
+      <c r="DA31" s="107"/>
+      <c r="DB31" s="108"/>
       <c r="DQ31" s="94" t="s">
         <v>126</v>
       </c>
@@ -23095,17 +23124,17 @@
       <c r="DB32" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="DF32" s="107" t="s">
+      <c r="DF32" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="DG32" s="108"/>
-      <c r="DH32" s="108"/>
-      <c r="DI32" s="108"/>
-      <c r="DJ32" s="108"/>
-      <c r="DK32" s="108"/>
-      <c r="DL32" s="108"/>
-      <c r="DM32" s="108"/>
-      <c r="DN32" s="109"/>
+      <c r="DG32" s="138"/>
+      <c r="DH32" s="138"/>
+      <c r="DI32" s="138"/>
+      <c r="DJ32" s="138"/>
+      <c r="DK32" s="138"/>
+      <c r="DL32" s="138"/>
+      <c r="DM32" s="138"/>
+      <c r="DN32" s="139"/>
       <c r="DQ32" s="94" t="s">
         <v>126</v>
       </c>
@@ -23279,14 +23308,14 @@
       <c r="DF33" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="DG33" s="104" t="s">
+      <c r="DG33" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="DH33" s="105"/>
-      <c r="DI33" s="105"/>
-      <c r="DJ33" s="105"/>
-      <c r="DK33" s="105"/>
-      <c r="DL33" s="106"/>
+      <c r="DH33" s="135"/>
+      <c r="DI33" s="135"/>
+      <c r="DJ33" s="135"/>
+      <c r="DK33" s="135"/>
+      <c r="DL33" s="136"/>
       <c r="DM33" s="90" t="s">
         <v>123</v>
       </c>
@@ -24734,23 +24763,23 @@
       </c>
     </row>
     <row r="46" spans="2:135" x14ac:dyDescent="0.2">
-      <c r="AD46" s="117"/>
-      <c r="AE46" s="117"/>
-      <c r="AF46" s="117"/>
-      <c r="AG46" s="117"/>
-      <c r="AH46" s="117"/>
-      <c r="AI46" s="117"/>
-      <c r="AJ46" s="117"/>
-      <c r="AK46" s="117"/>
-      <c r="AL46" s="117"/>
-      <c r="AM46" s="117"/>
-      <c r="AN46" s="117"/>
-      <c r="AO46" s="117"/>
-      <c r="AP46" s="117"/>
-      <c r="AQ46" s="117"/>
-      <c r="AR46" s="117"/>
-      <c r="AS46" s="117"/>
-      <c r="AT46" s="117"/>
+      <c r="AD46" s="112"/>
+      <c r="AE46" s="112"/>
+      <c r="AF46" s="112"/>
+      <c r="AG46" s="112"/>
+      <c r="AH46" s="112"/>
+      <c r="AI46" s="112"/>
+      <c r="AJ46" s="112"/>
+      <c r="AK46" s="112"/>
+      <c r="AL46" s="112"/>
+      <c r="AM46" s="112"/>
+      <c r="AN46" s="112"/>
+      <c r="AO46" s="112"/>
+      <c r="AP46" s="112"/>
+      <c r="AQ46" s="112"/>
+      <c r="AR46" s="112"/>
+      <c r="AS46" s="112"/>
+      <c r="AT46" s="112"/>
       <c r="CD46" t="s">
         <v>94</v>
       </c>
@@ -24780,22 +24809,22 @@
     </row>
     <row r="47" spans="2:135" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AD47" s="74"/>
-      <c r="AE47" s="117"/>
-      <c r="AF47" s="117"/>
-      <c r="AG47" s="117"/>
-      <c r="AH47" s="117"/>
-      <c r="AI47" s="117"/>
-      <c r="AJ47" s="117"/>
-      <c r="AK47" s="117"/>
-      <c r="AL47" s="117"/>
-      <c r="AM47" s="117"/>
-      <c r="AN47" s="117"/>
-      <c r="AO47" s="117"/>
-      <c r="AP47" s="117"/>
-      <c r="AQ47" s="117"/>
-      <c r="AR47" s="117"/>
-      <c r="AS47" s="117"/>
-      <c r="AT47" s="117"/>
+      <c r="AE47" s="112"/>
+      <c r="AF47" s="112"/>
+      <c r="AG47" s="112"/>
+      <c r="AH47" s="112"/>
+      <c r="AI47" s="112"/>
+      <c r="AJ47" s="112"/>
+      <c r="AK47" s="112"/>
+      <c r="AL47" s="112"/>
+      <c r="AM47" s="112"/>
+      <c r="AN47" s="112"/>
+      <c r="AO47" s="112"/>
+      <c r="AP47" s="112"/>
+      <c r="AQ47" s="112"/>
+      <c r="AR47" s="112"/>
+      <c r="AS47" s="112"/>
+      <c r="AT47" s="112"/>
       <c r="DQ47" s="94" t="s">
         <v>127</v>
       </c>
@@ -24821,21 +24850,21 @@
       </c>
     </row>
     <row r="48" spans="2:135" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O48" s="118" t="s">
+      <c r="O48" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="119"/>
-      <c r="Q48" s="119"/>
-      <c r="R48" s="119"/>
-      <c r="S48" s="119"/>
-      <c r="T48" s="119"/>
-      <c r="U48" s="119"/>
-      <c r="V48" s="119"/>
-      <c r="W48" s="119"/>
-      <c r="X48" s="119"/>
-      <c r="Y48" s="119"/>
-      <c r="Z48" s="119"/>
-      <c r="AA48" s="120"/>
+      <c r="P48" s="129"/>
+      <c r="Q48" s="129"/>
+      <c r="R48" s="129"/>
+      <c r="S48" s="129"/>
+      <c r="T48" s="129"/>
+      <c r="U48" s="129"/>
+      <c r="V48" s="129"/>
+      <c r="W48" s="129"/>
+      <c r="X48" s="129"/>
+      <c r="Y48" s="129"/>
+      <c r="Z48" s="129"/>
+      <c r="AA48" s="130"/>
       <c r="AE48" s="36"/>
       <c r="AF48" s="36"/>
       <c r="AG48" s="36"/>
@@ -24921,25 +24950,25 @@
       <c r="P49" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q49" s="121" t="s">
+      <c r="Q49" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="R49" s="122"/>
-      <c r="S49" s="123" t="s">
+      <c r="R49" s="127"/>
+      <c r="S49" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="T49" s="124"/>
-      <c r="U49" s="123" t="s">
+      <c r="T49" s="119"/>
+      <c r="U49" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="V49" s="125"/>
-      <c r="W49" s="123" t="s">
+      <c r="V49" s="120"/>
+      <c r="W49" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="X49" s="117"/>
-      <c r="Y49" s="117"/>
-      <c r="Z49" s="117"/>
-      <c r="AA49" s="125"/>
+      <c r="X49" s="112"/>
+      <c r="Y49" s="112"/>
+      <c r="Z49" s="112"/>
+      <c r="AA49" s="120"/>
       <c r="BM49">
         <v>2</v>
       </c>
@@ -25257,18 +25286,18 @@
         <f t="shared" ref="AA52:AA58" si="119">X52/Y52*100</f>
         <v>57.894736842105267</v>
       </c>
-      <c r="BO52" s="113" t="s">
+      <c r="BO52" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BP52" s="114"/>
-      <c r="BQ52" s="113" t="s">
+      <c r="BP52" s="105"/>
+      <c r="BQ52" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BR52" s="114"/>
-      <c r="BS52" s="113" t="s">
+      <c r="BR52" s="105"/>
+      <c r="BS52" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BT52" s="114"/>
+      <c r="BT52" s="105"/>
       <c r="DQ52" s="94" t="s">
         <v>127</v>
       </c>
@@ -26180,14 +26209,14 @@
       <c r="G60" t="s">
         <v>27</v>
       </c>
-      <c r="BO60" s="110" t="s">
+      <c r="BO60" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="BP60" s="111"/>
-      <c r="BQ60" s="111"/>
-      <c r="BR60" s="111"/>
-      <c r="BS60" s="111"/>
-      <c r="BT60" s="112"/>
+      <c r="BP60" s="107"/>
+      <c r="BQ60" s="107"/>
+      <c r="BR60" s="107"/>
+      <c r="BS60" s="107"/>
+      <c r="BT60" s="108"/>
       <c r="DQ60" s="94" t="s">
         <v>127</v>
       </c>
@@ -26558,20 +26587,20 @@
       </c>
     </row>
     <row r="69" spans="2:127" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="127" t="s">
+      <c r="B69" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="C69" s="128"/>
-      <c r="D69" s="128"/>
-      <c r="E69" s="128"/>
-      <c r="F69" s="128"/>
-      <c r="G69" s="128"/>
-      <c r="H69" s="128"/>
-      <c r="I69" s="128"/>
-      <c r="J69" s="128"/>
-      <c r="K69" s="128"/>
-      <c r="L69" s="128"/>
-      <c r="M69" s="129"/>
+      <c r="C69" s="116"/>
+      <c r="D69" s="116"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="116"/>
+      <c r="G69" s="116"/>
+      <c r="H69" s="116"/>
+      <c r="I69" s="116"/>
+      <c r="J69" s="116"/>
+      <c r="K69" s="116"/>
+      <c r="L69" s="116"/>
+      <c r="M69" s="117"/>
       <c r="BS69" t="s">
         <v>87</v>
       </c>
@@ -26603,25 +26632,25 @@
       <c r="B70" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C70" s="123" t="s">
+      <c r="C70" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="124"/>
-      <c r="E70" s="123" t="s">
+      <c r="D70" s="119"/>
+      <c r="E70" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="F70" s="124"/>
-      <c r="G70" s="123" t="s">
+      <c r="F70" s="119"/>
+      <c r="G70" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="H70" s="125"/>
-      <c r="I70" s="130" t="s">
+      <c r="H70" s="120"/>
+      <c r="I70" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="131"/>
-      <c r="K70" s="131"/>
-      <c r="L70" s="131"/>
-      <c r="M70" s="132"/>
+      <c r="J70" s="122"/>
+      <c r="K70" s="122"/>
+      <c r="L70" s="122"/>
+      <c r="M70" s="123"/>
       <c r="DQ70" s="94" t="s">
         <v>128</v>
       </c>
@@ -28905,18 +28934,18 @@
         <f>_xlfn.NORM.S.INV(G101)+5</f>
         <v>6.107002880537908</v>
       </c>
-      <c r="BO101" s="113" t="s">
+      <c r="BO101" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BP101" s="114"/>
-      <c r="BQ101" s="113" t="s">
+      <c r="BP101" s="105"/>
+      <c r="BQ101" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BR101" s="114"/>
-      <c r="BS101" s="113" t="s">
+      <c r="BR101" s="105"/>
+      <c r="BS101" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="BT101" s="114"/>
+      <c r="BT101" s="105"/>
     </row>
     <row r="102" spans="2:127" x14ac:dyDescent="0.2">
       <c r="BN102" s="43" t="s">
@@ -29153,14 +29182,14 @@
       <c r="BL109">
         <v>2.0833333333333335</v>
       </c>
-      <c r="BO109" s="110" t="s">
+      <c r="BO109" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="BP109" s="111"/>
-      <c r="BQ109" s="111"/>
-      <c r="BR109" s="111"/>
-      <c r="BS109" s="111"/>
-      <c r="BT109" s="112"/>
+      <c r="BP109" s="107"/>
+      <c r="BQ109" s="107"/>
+      <c r="BR109" s="107"/>
+      <c r="BS109" s="107"/>
+      <c r="BT109" s="108"/>
     </row>
     <row r="110" spans="2:127" x14ac:dyDescent="0.2">
       <c r="BN110" s="43" t="s">
@@ -29503,14 +29532,14 @@
       <c r="BL127">
         <v>2.0388888888888892</v>
       </c>
-      <c r="BO127" s="110" t="s">
+      <c r="BO127" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="BP127" s="111"/>
-      <c r="BQ127" s="111"/>
-      <c r="BR127" s="111"/>
-      <c r="BS127" s="111"/>
-      <c r="BT127" s="112"/>
+      <c r="BP127" s="107"/>
+      <c r="BQ127" s="107"/>
+      <c r="BR127" s="107"/>
+      <c r="BS127" s="107"/>
+      <c r="BT127" s="108"/>
     </row>
     <row r="128" spans="63:72" x14ac:dyDescent="0.2">
       <c r="BN128" s="43" t="s">
@@ -29636,22 +29665,46 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="CW5:CX5"/>
-    <mergeCell ref="CY5:CZ5"/>
-    <mergeCell ref="DA5:DB5"/>
-    <mergeCell ref="CW13:DB13"/>
-    <mergeCell ref="CW31:DB31"/>
-    <mergeCell ref="BO14:BZ14"/>
-    <mergeCell ref="AE5:AG5"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="AK5:AM5"/>
-    <mergeCell ref="AN5:AT5"/>
-    <mergeCell ref="BD6:BE6"/>
-    <mergeCell ref="AX5:BE5"/>
-    <mergeCell ref="AX12:BE12"/>
-    <mergeCell ref="AX6:AY6"/>
-    <mergeCell ref="AZ6:BA6"/>
-    <mergeCell ref="BB6:BC6"/>
+    <mergeCell ref="DR2:DW2"/>
+    <mergeCell ref="DX2:EC2"/>
+    <mergeCell ref="ED2:EI2"/>
+    <mergeCell ref="DG33:DL33"/>
+    <mergeCell ref="DF3:DN3"/>
+    <mergeCell ref="DF18:DN18"/>
+    <mergeCell ref="DF32:DN32"/>
+    <mergeCell ref="DG4:DL4"/>
+    <mergeCell ref="DG19:DL19"/>
+    <mergeCell ref="BO127:BT127"/>
+    <mergeCell ref="BO109:BT109"/>
+    <mergeCell ref="BO5:BZ5"/>
+    <mergeCell ref="BO101:BP101"/>
+    <mergeCell ref="BQ101:BR101"/>
+    <mergeCell ref="BS101:BT101"/>
+    <mergeCell ref="BO60:BT60"/>
+    <mergeCell ref="BY6:BZ6"/>
+    <mergeCell ref="BO52:BP52"/>
+    <mergeCell ref="BQ52:BR52"/>
+    <mergeCell ref="BS52:BT52"/>
+    <mergeCell ref="BW6:BX6"/>
+    <mergeCell ref="BO6:BP6"/>
+    <mergeCell ref="BQ6:BR6"/>
+    <mergeCell ref="BS6:BT6"/>
+    <mergeCell ref="BU6:BV6"/>
+    <mergeCell ref="AD46:AT46"/>
+    <mergeCell ref="AE47:AG47"/>
+    <mergeCell ref="AH47:AJ47"/>
+    <mergeCell ref="AK47:AM47"/>
+    <mergeCell ref="AN47:AT47"/>
+    <mergeCell ref="O48:AA48"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="S49:T49"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="W49:AA49"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:AA5"/>
+    <mergeCell ref="O4:AA4"/>
     <mergeCell ref="AD4:AT4"/>
     <mergeCell ref="B69:M69"/>
     <mergeCell ref="C70:D70"/>
@@ -29668,46 +29721,22 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="O4:AA4"/>
-    <mergeCell ref="O48:AA48"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="S49:T49"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="W49:AA49"/>
-    <mergeCell ref="AD46:AT46"/>
-    <mergeCell ref="AE47:AG47"/>
-    <mergeCell ref="AH47:AJ47"/>
-    <mergeCell ref="AK47:AM47"/>
-    <mergeCell ref="AN47:AT47"/>
-    <mergeCell ref="BO127:BT127"/>
-    <mergeCell ref="BO109:BT109"/>
-    <mergeCell ref="BO5:BZ5"/>
-    <mergeCell ref="BO101:BP101"/>
-    <mergeCell ref="BQ101:BR101"/>
-    <mergeCell ref="BS101:BT101"/>
-    <mergeCell ref="BO60:BT60"/>
-    <mergeCell ref="BY6:BZ6"/>
-    <mergeCell ref="BO52:BP52"/>
-    <mergeCell ref="BQ52:BR52"/>
-    <mergeCell ref="BS52:BT52"/>
-    <mergeCell ref="BW6:BX6"/>
-    <mergeCell ref="BO6:BP6"/>
-    <mergeCell ref="BQ6:BR6"/>
-    <mergeCell ref="BS6:BT6"/>
-    <mergeCell ref="BU6:BV6"/>
-    <mergeCell ref="DR2:DW2"/>
-    <mergeCell ref="DX2:EC2"/>
-    <mergeCell ref="ED2:EI2"/>
-    <mergeCell ref="DG33:DL33"/>
-    <mergeCell ref="DF3:DN3"/>
-    <mergeCell ref="DF18:DN18"/>
-    <mergeCell ref="DF32:DN32"/>
-    <mergeCell ref="DG4:DL4"/>
-    <mergeCell ref="DG19:DL19"/>
+    <mergeCell ref="BO14:BZ14"/>
+    <mergeCell ref="AE5:AG5"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="AK5:AM5"/>
+    <mergeCell ref="AN5:AT5"/>
+    <mergeCell ref="BD6:BE6"/>
+    <mergeCell ref="AX5:BE5"/>
+    <mergeCell ref="AX12:BE12"/>
+    <mergeCell ref="AX6:AY6"/>
+    <mergeCell ref="AZ6:BA6"/>
+    <mergeCell ref="BB6:BC6"/>
+    <mergeCell ref="CW5:CX5"/>
+    <mergeCell ref="CY5:CZ5"/>
+    <mergeCell ref="DA5:DB5"/>
+    <mergeCell ref="CW13:DB13"/>
+    <mergeCell ref="CW31:DB31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -32148,4 +32177,7638 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACCE994-2DF5-6843-9B1C-489B47B0DDB5}">
+  <dimension ref="A1:V97"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" s="99" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="100" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="101" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="P1" s="99" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="R1" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="S1" s="100" t="s">
+        <v>68</v>
+      </c>
+      <c r="T1" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="U1" s="101" t="s">
+        <v>44</v>
+      </c>
+      <c r="V1" s="102" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <f>D2-E2</f>
+        <v>13</v>
+      </c>
+      <c r="G2" s="95">
+        <f>E2/D2*100</f>
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>134</v>
+      </c>
+      <c r="P2" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q2" s="140">
+        <f>B2*143750</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="140">
+        <v>1</v>
+      </c>
+      <c r="S2" s="140">
+        <v>20</v>
+      </c>
+      <c r="T2" s="140">
+        <v>7</v>
+      </c>
+      <c r="U2" s="140">
+        <f>S2-T2</f>
+        <v>13</v>
+      </c>
+      <c r="V2" s="95">
+        <f>T2/S2*100</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>33</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F34" si="0">D3-E3</f>
+        <v>25</v>
+      </c>
+      <c r="G3" s="95">
+        <f t="shared" ref="G3:G34" si="1">E3/D3*100</f>
+        <v>24.242424242424242</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="56"/>
+      <c r="P3" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q3" s="140">
+        <f t="shared" ref="Q3:Q34" si="2">B3*143750</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="140">
+        <v>2</v>
+      </c>
+      <c r="S3" s="140">
+        <v>33</v>
+      </c>
+      <c r="T3" s="140">
+        <v>8</v>
+      </c>
+      <c r="U3" s="140">
+        <f t="shared" ref="U3:U34" si="3">S3-T3</f>
+        <v>25</v>
+      </c>
+      <c r="V3" s="95">
+        <f t="shared" ref="V3:V34" si="4">T3/S3*100</f>
+        <v>24.242424242424242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="G4" s="95">
+        <f t="shared" si="1"/>
+        <v>15.625</v>
+      </c>
+      <c r="I4" s="56">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <f>6.5*20*10^4</f>
+        <v>1300000</v>
+      </c>
+      <c r="K4" s="103">
+        <v>1120000</v>
+      </c>
+      <c r="M4">
+        <f>J5/J4*100</f>
+        <v>30.76923076923077</v>
+      </c>
+      <c r="N4" t="s">
+        <v>136</v>
+      </c>
+      <c r="P4" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q4" s="140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R4" s="140">
+        <v>3</v>
+      </c>
+      <c r="S4" s="140">
+        <v>32</v>
+      </c>
+      <c r="T4" s="140">
+        <v>5</v>
+      </c>
+      <c r="U4" s="140">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="V4" s="95">
+        <f t="shared" si="4"/>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G5" s="95">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="I5" s="56">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f>2*20*10^4</f>
+        <v>400000</v>
+      </c>
+      <c r="K5" s="103">
+        <v>480000</v>
+      </c>
+      <c r="P5" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q5" s="140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="140">
+        <v>4</v>
+      </c>
+      <c r="S5" s="140">
+        <v>30</v>
+      </c>
+      <c r="T5" s="140">
+        <v>2</v>
+      </c>
+      <c r="U5" s="140">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="V5" s="95">
+        <f t="shared" si="4"/>
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="G6" s="95">
+        <f t="shared" si="1"/>
+        <v>22.857142857142858</v>
+      </c>
+      <c r="P6" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q6" s="140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="140">
+        <v>5</v>
+      </c>
+      <c r="S6" s="140">
+        <v>35</v>
+      </c>
+      <c r="T6" s="140">
+        <v>8</v>
+      </c>
+      <c r="U6" s="140">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="V6" s="95">
+        <f t="shared" si="4"/>
+        <v>22.857142857142858</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G7" s="95">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
+        <v>138</v>
+      </c>
+      <c r="P7" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q7" s="140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="140">
+        <v>6</v>
+      </c>
+      <c r="S7" s="140">
+        <v>35</v>
+      </c>
+      <c r="T7" s="140">
+        <v>7</v>
+      </c>
+      <c r="U7" s="140">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="V7" s="95">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8">
+        <v>0.53</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G8" s="95">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L8">
+        <f>K4/704</f>
+        <v>1590.909090909091</v>
+      </c>
+      <c r="P8" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q8" s="140">
+        <f t="shared" si="2"/>
+        <v>76187.5</v>
+      </c>
+      <c r="R8" s="140">
+        <v>1</v>
+      </c>
+      <c r="S8" s="140">
+        <v>25</v>
+      </c>
+      <c r="T8" s="140">
+        <v>6</v>
+      </c>
+      <c r="U8" s="140">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="V8" s="95">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9">
+        <v>0.53</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G9" s="95">
+        <f t="shared" si="1"/>
+        <v>19.047619047619047</v>
+      </c>
+      <c r="P9" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q9" s="140">
+        <f t="shared" si="2"/>
+        <v>76187.5</v>
+      </c>
+      <c r="R9" s="140">
+        <v>2</v>
+      </c>
+      <c r="S9" s="140">
+        <v>21</v>
+      </c>
+      <c r="T9" s="140">
+        <v>4</v>
+      </c>
+      <c r="U9" s="140">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="V9" s="95">
+        <f t="shared" si="4"/>
+        <v>19.047619047619047</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10">
+        <v>0.53</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="G10" s="95">
+        <f t="shared" si="1"/>
+        <v>24.390243902439025</v>
+      </c>
+      <c r="I10" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q10" s="140">
+        <f t="shared" si="2"/>
+        <v>76187.5</v>
+      </c>
+      <c r="R10" s="140">
+        <v>3</v>
+      </c>
+      <c r="S10" s="140">
+        <v>41</v>
+      </c>
+      <c r="T10" s="140">
+        <v>10</v>
+      </c>
+      <c r="U10" s="140">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="V10" s="95">
+        <f t="shared" si="4"/>
+        <v>24.390243902439025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11">
+        <v>1.6</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G11" s="95">
+        <f t="shared" si="1"/>
+        <v>29.629629629629626</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="74"/>
+      <c r="P11" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q11" s="140">
+        <f t="shared" si="2"/>
+        <v>230000</v>
+      </c>
+      <c r="R11" s="140">
+        <v>1</v>
+      </c>
+      <c r="S11" s="140">
+        <v>27</v>
+      </c>
+      <c r="T11" s="140">
+        <v>8</v>
+      </c>
+      <c r="U11" s="140">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="V11" s="95">
+        <f t="shared" si="4"/>
+        <v>29.629629629629626</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12">
+        <v>1.6</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G12" s="95">
+        <f t="shared" si="1"/>
+        <v>29.166666666666668</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f>5.75*20*10^4</f>
+        <v>1150000</v>
+      </c>
+      <c r="K12" s="103">
+        <v>1150000</v>
+      </c>
+      <c r="M12">
+        <f>J13/J12</f>
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="N12" t="s">
+        <v>137</v>
+      </c>
+      <c r="P12" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q12" s="140">
+        <f t="shared" si="2"/>
+        <v>230000</v>
+      </c>
+      <c r="R12" s="140">
+        <v>2</v>
+      </c>
+      <c r="S12" s="140">
+        <v>24</v>
+      </c>
+      <c r="T12" s="140">
+        <v>7</v>
+      </c>
+      <c r="U12" s="140">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="V12" s="95">
+        <f t="shared" si="4"/>
+        <v>29.166666666666668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13">
+        <v>1.6</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>38</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="G13" s="95">
+        <f t="shared" si="1"/>
+        <v>31.578947368421051</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <f>2*20*10^4</f>
+        <v>400000</v>
+      </c>
+      <c r="K13" s="103">
+        <v>400000</v>
+      </c>
+      <c r="P13" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q13" s="140">
+        <f t="shared" si="2"/>
+        <v>230000</v>
+      </c>
+      <c r="R13" s="140">
+        <v>3</v>
+      </c>
+      <c r="S13" s="140">
+        <v>38</v>
+      </c>
+      <c r="T13" s="140">
+        <v>12</v>
+      </c>
+      <c r="U13" s="140">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="V13" s="95">
+        <f t="shared" si="4"/>
+        <v>31.578947368421051</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G14" s="95">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="P14" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q14" s="140">
+        <f t="shared" si="2"/>
+        <v>632500</v>
+      </c>
+      <c r="R14" s="140">
+        <v>1</v>
+      </c>
+      <c r="S14" s="140">
+        <v>24</v>
+      </c>
+      <c r="T14" s="140">
+        <v>6</v>
+      </c>
+      <c r="U14" s="140">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="V14" s="95">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>62</v>
+      </c>
+      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="G15" s="95">
+        <f t="shared" si="1"/>
+        <v>41.935483870967744</v>
+      </c>
+      <c r="I15" t="s">
+        <v>138</v>
+      </c>
+      <c r="P15" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q15" s="140">
+        <f t="shared" si="2"/>
+        <v>632500</v>
+      </c>
+      <c r="R15" s="140">
+        <v>2</v>
+      </c>
+      <c r="S15" s="140">
+        <v>62</v>
+      </c>
+      <c r="T15" s="140">
+        <v>26</v>
+      </c>
+      <c r="U15" s="140">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="V15" s="95">
+        <f t="shared" si="4"/>
+        <v>41.935483870967744</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G16" s="95">
+        <f t="shared" si="1"/>
+        <v>28.571428571428569</v>
+      </c>
+      <c r="I16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K16" t="s">
+        <v>144</v>
+      </c>
+      <c r="L16">
+        <f>K12/1333</f>
+        <v>862.71567891972995</v>
+      </c>
+      <c r="P16" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q16" s="140">
+        <f t="shared" si="2"/>
+        <v>632500</v>
+      </c>
+      <c r="R16" s="140">
+        <v>3</v>
+      </c>
+      <c r="S16" s="140">
+        <v>28</v>
+      </c>
+      <c r="T16" s="140">
+        <v>8</v>
+      </c>
+      <c r="U16" s="140">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="V16" s="95">
+        <f t="shared" si="4"/>
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17">
+        <v>4.7</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G17" s="95">
+        <f t="shared" si="1"/>
+        <v>42.857142857142854</v>
+      </c>
+      <c r="P17" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q17" s="140">
+        <f t="shared" si="2"/>
+        <v>675625</v>
+      </c>
+      <c r="R17" s="140">
+        <v>1</v>
+      </c>
+      <c r="S17" s="140">
+        <v>21</v>
+      </c>
+      <c r="T17" s="140">
+        <v>9</v>
+      </c>
+      <c r="U17" s="140">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V17" s="95">
+        <f t="shared" si="4"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18">
+        <v>4.7</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>57</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G18" s="95">
+        <f t="shared" si="1"/>
+        <v>26.315789473684209</v>
+      </c>
+      <c r="I18" t="s">
+        <v>135</v>
+      </c>
+      <c r="P18" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q18" s="140">
+        <f t="shared" si="2"/>
+        <v>675625</v>
+      </c>
+      <c r="R18" s="140">
+        <v>2</v>
+      </c>
+      <c r="S18" s="140">
+        <v>57</v>
+      </c>
+      <c r="T18" s="140">
+        <v>15</v>
+      </c>
+      <c r="U18" s="140">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="V18" s="95">
+        <f t="shared" si="4"/>
+        <v>26.315789473684209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19">
+        <v>4.7</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>67</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="G19" s="95">
+        <f t="shared" si="1"/>
+        <v>28.35820895522388</v>
+      </c>
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+      <c r="P19" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q19" s="140">
+        <f t="shared" si="2"/>
+        <v>675625</v>
+      </c>
+      <c r="R19" s="140">
+        <v>3</v>
+      </c>
+      <c r="S19" s="140">
+        <v>67</v>
+      </c>
+      <c r="T19" s="140">
+        <v>19</v>
+      </c>
+      <c r="U19" s="140">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="V19" s="95">
+        <f t="shared" si="4"/>
+        <v>28.35820895522388</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G20" s="95">
+        <f t="shared" si="1"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J20">
+        <f>28.75*20*(10^4)</f>
+        <v>5750000</v>
+      </c>
+      <c r="K20" s="103">
+        <v>5750000</v>
+      </c>
+      <c r="M20">
+        <f>J21/J20</f>
+        <v>0.36521739130434783</v>
+      </c>
+      <c r="N20" t="s">
+        <v>137</v>
+      </c>
+      <c r="P20" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q20" s="140">
+        <f t="shared" si="2"/>
+        <v>1868750</v>
+      </c>
+      <c r="R20" s="140">
+        <v>1</v>
+      </c>
+      <c r="S20" s="140">
+        <v>15</v>
+      </c>
+      <c r="T20" s="140">
+        <v>5</v>
+      </c>
+      <c r="U20" s="140">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="V20" s="95">
+        <f t="shared" si="4"/>
+        <v>33.333333333333329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>43</v>
+      </c>
+      <c r="E21">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="G21" s="95">
+        <f t="shared" si="1"/>
+        <v>37.209302325581397</v>
+      </c>
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21">
+        <f>10.5*20*(10^4)</f>
+        <v>2100000</v>
+      </c>
+      <c r="K21" s="103">
+        <v>2100000</v>
+      </c>
+      <c r="P21" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q21" s="140">
+        <f t="shared" si="2"/>
+        <v>1868750</v>
+      </c>
+      <c r="R21" s="140">
+        <v>2</v>
+      </c>
+      <c r="S21" s="140">
+        <v>43</v>
+      </c>
+      <c r="T21" s="140">
+        <v>16</v>
+      </c>
+      <c r="U21" s="140">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="V21" s="95">
+        <f t="shared" si="4"/>
+        <v>37.209302325581397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>64</v>
+      </c>
+      <c r="E22">
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="G22" s="95">
+        <f t="shared" si="1"/>
+        <v>31.25</v>
+      </c>
+      <c r="P22" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q22" s="140">
+        <f t="shared" si="2"/>
+        <v>1868750</v>
+      </c>
+      <c r="R22" s="140">
+        <v>3</v>
+      </c>
+      <c r="S22" s="140">
+        <v>64</v>
+      </c>
+      <c r="T22" s="140">
+        <v>20</v>
+      </c>
+      <c r="U22" s="140">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="V22" s="95">
+        <f t="shared" si="4"/>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A23" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>13</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G23" s="95">
+        <f t="shared" si="1"/>
+        <v>46.153846153846153</v>
+      </c>
+      <c r="I23" t="s">
+        <v>138</v>
+      </c>
+      <c r="P23" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q23" s="140">
+        <f t="shared" si="2"/>
+        <v>2012500</v>
+      </c>
+      <c r="R23" s="140">
+        <v>1</v>
+      </c>
+      <c r="S23" s="140">
+        <v>13</v>
+      </c>
+      <c r="T23" s="140">
+        <v>6</v>
+      </c>
+      <c r="U23" s="140">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="V23" s="95">
+        <f t="shared" si="4"/>
+        <v>46.153846153846153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A24" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>50</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="G24" s="95">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="I24" t="s">
+        <v>139</v>
+      </c>
+      <c r="K24" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24">
+        <f>5750000/40</f>
+        <v>143750</v>
+      </c>
+      <c r="M24" t="s">
+        <v>141</v>
+      </c>
+      <c r="P24" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q24" s="140">
+        <f t="shared" si="2"/>
+        <v>2012500</v>
+      </c>
+      <c r="R24" s="140">
+        <v>2</v>
+      </c>
+      <c r="S24" s="140">
+        <v>50</v>
+      </c>
+      <c r="T24" s="140">
+        <v>17</v>
+      </c>
+      <c r="U24" s="140">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="V24" s="95">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A25" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>49</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="G25" s="95">
+        <f t="shared" si="1"/>
+        <v>36.734693877551024</v>
+      </c>
+      <c r="P25" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q25" s="140">
+        <f t="shared" si="2"/>
+        <v>2012500</v>
+      </c>
+      <c r="R25" s="140">
+        <v>3</v>
+      </c>
+      <c r="S25" s="140">
+        <v>49</v>
+      </c>
+      <c r="T25" s="140">
+        <v>18</v>
+      </c>
+      <c r="U25" s="140">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="V25" s="95">
+        <f t="shared" si="4"/>
+        <v>36.734693877551024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G26" s="95">
+        <f t="shared" si="1"/>
+        <v>38.095238095238095</v>
+      </c>
+      <c r="P26" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q26" s="140">
+        <f t="shared" si="2"/>
+        <v>5750000</v>
+      </c>
+      <c r="R26" s="140">
+        <v>1</v>
+      </c>
+      <c r="S26" s="140">
+        <v>21</v>
+      </c>
+      <c r="T26" s="140">
+        <v>8</v>
+      </c>
+      <c r="U26" s="140">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="V26" s="95">
+        <f t="shared" si="4"/>
+        <v>38.095238095238095</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A27" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>54</v>
+      </c>
+      <c r="E27">
+        <v>21</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="G27" s="95">
+        <f t="shared" si="1"/>
+        <v>38.888888888888893</v>
+      </c>
+      <c r="P27" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q27" s="140">
+        <f t="shared" si="2"/>
+        <v>5750000</v>
+      </c>
+      <c r="R27" s="140">
+        <v>2</v>
+      </c>
+      <c r="S27" s="140">
+        <v>54</v>
+      </c>
+      <c r="T27" s="140">
+        <v>21</v>
+      </c>
+      <c r="U27" s="140">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="V27" s="95">
+        <f t="shared" si="4"/>
+        <v>38.888888888888893</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>59</v>
+      </c>
+      <c r="E28">
+        <v>22</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="G28" s="95">
+        <f t="shared" si="1"/>
+        <v>37.288135593220339</v>
+      </c>
+      <c r="P28" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q28" s="140">
+        <f t="shared" si="2"/>
+        <v>5750000</v>
+      </c>
+      <c r="R28" s="140">
+        <v>3</v>
+      </c>
+      <c r="S28" s="140">
+        <v>59</v>
+      </c>
+      <c r="T28" s="140">
+        <v>22</v>
+      </c>
+      <c r="U28" s="140">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="V28" s="95">
+        <f t="shared" si="4"/>
+        <v>37.288135593220339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29">
+        <v>43</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>11</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G29" s="95">
+        <f t="shared" si="1"/>
+        <v>63.636363636363633</v>
+      </c>
+      <c r="P29" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q29" s="140">
+        <f t="shared" si="2"/>
+        <v>6181250</v>
+      </c>
+      <c r="R29" s="140">
+        <v>1</v>
+      </c>
+      <c r="S29" s="140">
+        <v>11</v>
+      </c>
+      <c r="T29" s="140">
+        <v>7</v>
+      </c>
+      <c r="U29" s="140">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="V29" s="95">
+        <f t="shared" si="4"/>
+        <v>63.636363636363633</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30">
+        <v>43</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>46</v>
+      </c>
+      <c r="E30">
+        <v>16</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="G30" s="95">
+        <f t="shared" si="1"/>
+        <v>34.782608695652172</v>
+      </c>
+      <c r="P30" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q30" s="140">
+        <f t="shared" si="2"/>
+        <v>6181250</v>
+      </c>
+      <c r="R30" s="140">
+        <v>2</v>
+      </c>
+      <c r="S30" s="140">
+        <v>46</v>
+      </c>
+      <c r="T30" s="140">
+        <v>16</v>
+      </c>
+      <c r="U30" s="140">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="V30" s="95">
+        <f t="shared" si="4"/>
+        <v>34.782608695652172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31">
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>19</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G31" s="95">
+        <f t="shared" si="1"/>
+        <v>36.84210526315789</v>
+      </c>
+      <c r="P31" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q31" s="140">
+        <f t="shared" si="2"/>
+        <v>6181250</v>
+      </c>
+      <c r="R31" s="140">
+        <v>3</v>
+      </c>
+      <c r="S31" s="140">
+        <v>19</v>
+      </c>
+      <c r="T31" s="140">
+        <v>7</v>
+      </c>
+      <c r="U31" s="140">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V31" s="95">
+        <f t="shared" si="4"/>
+        <v>36.84210526315789</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32">
+        <v>120</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>22</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G32" s="95">
+        <f t="shared" si="1"/>
+        <v>45.454545454545453</v>
+      </c>
+      <c r="P32" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q32" s="140">
+        <f t="shared" si="2"/>
+        <v>17250000</v>
+      </c>
+      <c r="R32" s="140">
+        <v>1</v>
+      </c>
+      <c r="S32" s="140">
+        <v>22</v>
+      </c>
+      <c r="T32" s="140">
+        <v>10</v>
+      </c>
+      <c r="U32" s="140">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V32" s="95">
+        <f t="shared" si="4"/>
+        <v>45.454545454545453</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33">
+        <v>120</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>38</v>
+      </c>
+      <c r="E33">
+        <v>12</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="G33" s="95">
+        <f t="shared" si="1"/>
+        <v>31.578947368421051</v>
+      </c>
+      <c r="P33" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q33" s="140">
+        <f t="shared" si="2"/>
+        <v>17250000</v>
+      </c>
+      <c r="R33" s="140">
+        <v>2</v>
+      </c>
+      <c r="S33" s="140">
+        <v>38</v>
+      </c>
+      <c r="T33" s="140">
+        <v>12</v>
+      </c>
+      <c r="U33" s="140">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="V33" s="95">
+        <f t="shared" si="4"/>
+        <v>31.578947368421051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34">
+        <v>120</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>40</v>
+      </c>
+      <c r="E34">
+        <v>14</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="G34" s="95">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="P34" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q34" s="140">
+        <f t="shared" si="2"/>
+        <v>17250000</v>
+      </c>
+      <c r="R34" s="140">
+        <v>3</v>
+      </c>
+      <c r="S34" s="140">
+        <v>40</v>
+      </c>
+      <c r="T34" s="140">
+        <v>14</v>
+      </c>
+      <c r="U34" s="140">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="V34" s="95">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>23</v>
+      </c>
+      <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="F35">
+        <f>D35-E35</f>
+        <v>10</v>
+      </c>
+      <c r="G35" s="95">
+        <f>E35/D35*100</f>
+        <v>56.521739130434781</v>
+      </c>
+      <c r="P35" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q35" s="140">
+        <f>B35*1591</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="140">
+        <v>1</v>
+      </c>
+      <c r="S35" s="140">
+        <v>23</v>
+      </c>
+      <c r="T35" s="140">
+        <v>13</v>
+      </c>
+      <c r="U35" s="140">
+        <f>S35-T35</f>
+        <v>10</v>
+      </c>
+      <c r="V35" s="95">
+        <f>T35/S35*100</f>
+        <v>56.521739130434781</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>34</v>
+      </c>
+      <c r="E36">
+        <v>12</v>
+      </c>
+      <c r="F36">
+        <f>D36-E36</f>
+        <v>22</v>
+      </c>
+      <c r="G36" s="95">
+        <f>E36/D36*100</f>
+        <v>35.294117647058826</v>
+      </c>
+      <c r="P36" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q36" s="140">
+        <f t="shared" ref="Q36:Q64" si="5">B36*1591</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="140">
+        <v>2</v>
+      </c>
+      <c r="S36" s="140">
+        <v>34</v>
+      </c>
+      <c r="T36" s="140">
+        <v>12</v>
+      </c>
+      <c r="U36" s="140">
+        <f>S36-T36</f>
+        <v>22</v>
+      </c>
+      <c r="V36" s="95">
+        <f>T36/S36*100</f>
+        <v>35.294117647058826</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>18</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="F37">
+        <f t="shared" ref="F37:F64" si="6">D37-E37</f>
+        <v>11</v>
+      </c>
+      <c r="G37" s="95">
+        <f t="shared" ref="G37:G64" si="7">E37/D37*100</f>
+        <v>38.888888888888893</v>
+      </c>
+      <c r="P37" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q37" s="140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="140">
+        <v>3</v>
+      </c>
+      <c r="S37" s="140">
+        <v>18</v>
+      </c>
+      <c r="T37" s="140">
+        <v>7</v>
+      </c>
+      <c r="U37" s="140">
+        <f t="shared" ref="U37:U64" si="8">S37-T37</f>
+        <v>11</v>
+      </c>
+      <c r="V37" s="95">
+        <f t="shared" ref="V37:V64" si="9">T37/S37*100</f>
+        <v>38.888888888888893</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>22</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="G38" s="95">
+        <f t="shared" si="7"/>
+        <v>18.181818181818183</v>
+      </c>
+      <c r="P38" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q38" s="140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="140">
+        <v>4</v>
+      </c>
+      <c r="S38" s="140">
+        <v>22</v>
+      </c>
+      <c r="T38" s="140">
+        <v>4</v>
+      </c>
+      <c r="U38" s="140">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="V38" s="95">
+        <f t="shared" si="9"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>22</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="G39" s="95">
+        <f t="shared" si="7"/>
+        <v>18.181818181818183</v>
+      </c>
+      <c r="P39" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q39" s="140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R39" s="140">
+        <v>5</v>
+      </c>
+      <c r="S39" s="140">
+        <v>22</v>
+      </c>
+      <c r="T39" s="140">
+        <v>4</v>
+      </c>
+      <c r="U39" s="140">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="V39" s="95">
+        <f t="shared" si="9"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="G40" s="95">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="P40" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q40" s="140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="140">
+        <v>6</v>
+      </c>
+      <c r="S40" s="140">
+        <v>20</v>
+      </c>
+      <c r="T40" s="140">
+        <v>4</v>
+      </c>
+      <c r="U40" s="140">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="V40" s="95">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41">
+        <v>76</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>7</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="G41" s="95">
+        <f t="shared" si="7"/>
+        <v>30.434782608695656</v>
+      </c>
+      <c r="P41" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q41" s="140">
+        <f t="shared" si="5"/>
+        <v>120916</v>
+      </c>
+      <c r="R41" s="140">
+        <v>1</v>
+      </c>
+      <c r="S41" s="140">
+        <v>23</v>
+      </c>
+      <c r="T41" s="140">
+        <v>7</v>
+      </c>
+      <c r="U41" s="140">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="V41" s="95">
+        <f t="shared" si="9"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42">
+        <v>76</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>22</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="G42" s="95">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="P42" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q42" s="140">
+        <f t="shared" si="5"/>
+        <v>120916</v>
+      </c>
+      <c r="R42" s="140">
+        <v>2</v>
+      </c>
+      <c r="S42" s="140">
+        <v>22</v>
+      </c>
+      <c r="T42" s="140">
+        <v>11</v>
+      </c>
+      <c r="U42" s="140">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="V42" s="95">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43">
+        <v>76</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>23</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="G43" s="95">
+        <f t="shared" si="7"/>
+        <v>30.434782608695656</v>
+      </c>
+      <c r="P43" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q43" s="140">
+        <f t="shared" si="5"/>
+        <v>120916</v>
+      </c>
+      <c r="R43" s="140">
+        <v>3</v>
+      </c>
+      <c r="S43" s="140">
+        <v>23</v>
+      </c>
+      <c r="T43" s="140">
+        <v>7</v>
+      </c>
+      <c r="U43" s="140">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="V43" s="95">
+        <f t="shared" si="9"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44">
+        <v>78</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>19</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="G44" s="95">
+        <f t="shared" si="7"/>
+        <v>21.052631578947366</v>
+      </c>
+      <c r="P44" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q44" s="140">
+        <f t="shared" si="5"/>
+        <v>124098</v>
+      </c>
+      <c r="R44" s="140">
+        <v>1</v>
+      </c>
+      <c r="S44" s="140">
+        <v>19</v>
+      </c>
+      <c r="T44" s="140">
+        <v>4</v>
+      </c>
+      <c r="U44" s="140">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="V44" s="95">
+        <f t="shared" si="9"/>
+        <v>21.052631578947366</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45">
+        <v>78</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>16</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="G45" s="95">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="P45" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q45" s="140">
+        <f t="shared" si="5"/>
+        <v>124098</v>
+      </c>
+      <c r="R45" s="140">
+        <v>2</v>
+      </c>
+      <c r="S45" s="140">
+        <v>16</v>
+      </c>
+      <c r="T45" s="140">
+        <v>4</v>
+      </c>
+      <c r="U45" s="140">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="V45" s="95">
+        <f t="shared" si="9"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46">
+        <v>78</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>23</v>
+      </c>
+      <c r="E46">
+        <v>7</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="G46" s="95">
+        <f t="shared" si="7"/>
+        <v>30.434782608695656</v>
+      </c>
+      <c r="P46" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q46" s="140">
+        <f t="shared" si="5"/>
+        <v>124098</v>
+      </c>
+      <c r="R46" s="140">
+        <v>3</v>
+      </c>
+      <c r="S46" s="140">
+        <v>23</v>
+      </c>
+      <c r="T46" s="140">
+        <v>7</v>
+      </c>
+      <c r="U46" s="140">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="V46" s="95">
+        <f t="shared" si="9"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47">
+        <v>227</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="G47" s="95">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="P47" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q47" s="140">
+        <f t="shared" si="5"/>
+        <v>361157</v>
+      </c>
+      <c r="R47" s="140">
+        <v>1</v>
+      </c>
+      <c r="S47" s="140">
+        <v>10</v>
+      </c>
+      <c r="T47" s="140">
+        <v>4</v>
+      </c>
+      <c r="U47" s="140">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="V47" s="95">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48">
+        <v>227</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>26</v>
+      </c>
+      <c r="E48">
+        <v>11</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="G48" s="95">
+        <f t="shared" si="7"/>
+        <v>42.307692307692307</v>
+      </c>
+      <c r="P48" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q48" s="140">
+        <f t="shared" si="5"/>
+        <v>361157</v>
+      </c>
+      <c r="R48" s="140">
+        <v>2</v>
+      </c>
+      <c r="S48" s="140">
+        <v>26</v>
+      </c>
+      <c r="T48" s="140">
+        <v>11</v>
+      </c>
+      <c r="U48" s="140">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="V48" s="95">
+        <f t="shared" si="9"/>
+        <v>42.307692307692307</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49">
+        <v>227</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
+        <v>26</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="G49" s="95">
+        <f t="shared" si="7"/>
+        <v>38.461538461538467</v>
+      </c>
+      <c r="P49" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q49" s="140">
+        <f t="shared" si="5"/>
+        <v>361157</v>
+      </c>
+      <c r="R49" s="140">
+        <v>3</v>
+      </c>
+      <c r="S49" s="140">
+        <v>26</v>
+      </c>
+      <c r="T49" s="140">
+        <v>10</v>
+      </c>
+      <c r="U49" s="140">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="V49" s="95">
+        <f t="shared" si="9"/>
+        <v>38.461538461538467</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50">
+        <v>235</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>20</v>
+      </c>
+      <c r="E50">
+        <v>7</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="G50" s="95">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="P50" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q50" s="140">
+        <f t="shared" si="5"/>
+        <v>373885</v>
+      </c>
+      <c r="R50" s="140">
+        <v>1</v>
+      </c>
+      <c r="S50" s="140">
+        <v>20</v>
+      </c>
+      <c r="T50" s="140">
+        <v>7</v>
+      </c>
+      <c r="U50" s="140">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="V50" s="95">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A51" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51">
+        <v>235</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>22</v>
+      </c>
+      <c r="E51">
+        <v>7</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="G51" s="95">
+        <f t="shared" si="7"/>
+        <v>31.818181818181817</v>
+      </c>
+      <c r="P51" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q51" s="140">
+        <f t="shared" si="5"/>
+        <v>373885</v>
+      </c>
+      <c r="R51" s="140">
+        <v>2</v>
+      </c>
+      <c r="S51" s="140">
+        <v>22</v>
+      </c>
+      <c r="T51" s="140">
+        <v>7</v>
+      </c>
+      <c r="U51" s="140">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="V51" s="95">
+        <f t="shared" si="9"/>
+        <v>31.818181818181817</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52">
+        <v>235</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>28</v>
+      </c>
+      <c r="E52">
+        <v>7</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="G52" s="95">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="P52" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q52" s="140">
+        <f t="shared" si="5"/>
+        <v>373885</v>
+      </c>
+      <c r="R52" s="140">
+        <v>3</v>
+      </c>
+      <c r="S52" s="140">
+        <v>28</v>
+      </c>
+      <c r="T52" s="140">
+        <v>7</v>
+      </c>
+      <c r="U52" s="140">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="V52" s="95">
+        <f t="shared" si="9"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53">
+        <v>680</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>37</v>
+      </c>
+      <c r="E53">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="G53" s="95">
+        <f t="shared" si="7"/>
+        <v>54.054054054054056</v>
+      </c>
+      <c r="P53" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q53" s="140">
+        <f t="shared" si="5"/>
+        <v>1081880</v>
+      </c>
+      <c r="R53" s="140">
+        <v>1</v>
+      </c>
+      <c r="S53" s="140">
+        <v>37</v>
+      </c>
+      <c r="T53" s="140">
+        <v>20</v>
+      </c>
+      <c r="U53" s="140">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+      <c r="V53" s="95">
+        <f t="shared" si="9"/>
+        <v>54.054054054054056</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A54" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54">
+        <v>680</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>28</v>
+      </c>
+      <c r="E54">
+        <v>13</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="G54" s="95">
+        <f t="shared" si="7"/>
+        <v>46.428571428571431</v>
+      </c>
+      <c r="P54" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q54" s="140">
+        <f t="shared" si="5"/>
+        <v>1081880</v>
+      </c>
+      <c r="R54" s="140">
+        <v>2</v>
+      </c>
+      <c r="S54" s="140">
+        <v>28</v>
+      </c>
+      <c r="T54" s="140">
+        <v>13</v>
+      </c>
+      <c r="U54" s="140">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="V54" s="95">
+        <f t="shared" si="9"/>
+        <v>46.428571428571431</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A55" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55">
+        <v>680</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="G55" s="95">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="P55" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q55" s="140">
+        <f t="shared" si="5"/>
+        <v>1081880</v>
+      </c>
+      <c r="R55" s="140">
+        <v>3</v>
+      </c>
+      <c r="S55" s="140">
+        <v>12</v>
+      </c>
+      <c r="T55" s="140">
+        <v>3</v>
+      </c>
+      <c r="U55" s="140">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="V55" s="95">
+        <f t="shared" si="9"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A56" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56">
+        <v>704</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>18</v>
+      </c>
+      <c r="E56">
+        <v>8</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="G56" s="95">
+        <f t="shared" si="7"/>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="P56" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q56" s="140">
+        <f t="shared" si="5"/>
+        <v>1120064</v>
+      </c>
+      <c r="R56" s="140">
+        <v>1</v>
+      </c>
+      <c r="S56" s="140">
+        <v>18</v>
+      </c>
+      <c r="T56" s="140">
+        <v>8</v>
+      </c>
+      <c r="U56" s="140">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="V56" s="95">
+        <f t="shared" si="9"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A57" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57">
+        <v>704</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>19</v>
+      </c>
+      <c r="E57">
+        <v>7</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="G57" s="95">
+        <f t="shared" si="7"/>
+        <v>36.84210526315789</v>
+      </c>
+      <c r="P57" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q57" s="140">
+        <f t="shared" si="5"/>
+        <v>1120064</v>
+      </c>
+      <c r="R57" s="140">
+        <v>2</v>
+      </c>
+      <c r="S57" s="140">
+        <v>19</v>
+      </c>
+      <c r="T57" s="140">
+        <v>7</v>
+      </c>
+      <c r="U57" s="140">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="V57" s="95">
+        <f t="shared" si="9"/>
+        <v>36.84210526315789</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A58" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58">
+        <v>704</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>35</v>
+      </c>
+      <c r="E58">
+        <v>14</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="G58" s="95">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="P58" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q58" s="140">
+        <f t="shared" si="5"/>
+        <v>1120064</v>
+      </c>
+      <c r="R58" s="140">
+        <v>3</v>
+      </c>
+      <c r="S58" s="140">
+        <v>35</v>
+      </c>
+      <c r="T58" s="140">
+        <v>14</v>
+      </c>
+      <c r="U58" s="140">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="V58" s="95">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A59" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59">
+        <v>2049</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>16</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="G59" s="95">
+        <f t="shared" si="7"/>
+        <v>37.5</v>
+      </c>
+      <c r="P59" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q59" s="140">
+        <f t="shared" si="5"/>
+        <v>3259959</v>
+      </c>
+      <c r="R59" s="140">
+        <v>1</v>
+      </c>
+      <c r="S59" s="140">
+        <v>16</v>
+      </c>
+      <c r="T59" s="140">
+        <v>6</v>
+      </c>
+      <c r="U59" s="140">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="V59" s="95">
+        <f t="shared" si="9"/>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A60" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60">
+        <v>2049</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>18</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="G60" s="95">
+        <f t="shared" si="7"/>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="P60" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q60" s="140">
+        <f t="shared" si="5"/>
+        <v>3259959</v>
+      </c>
+      <c r="R60" s="140">
+        <v>2</v>
+      </c>
+      <c r="S60" s="140">
+        <v>18</v>
+      </c>
+      <c r="T60" s="140">
+        <v>8</v>
+      </c>
+      <c r="U60" s="140">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="V60" s="95">
+        <f t="shared" si="9"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A61" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61">
+        <v>2049</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>16</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="G61" s="95">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="P61" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q61" s="140">
+        <f t="shared" si="5"/>
+        <v>3259959</v>
+      </c>
+      <c r="R61" s="140">
+        <v>3</v>
+      </c>
+      <c r="S61" s="140">
+        <v>16</v>
+      </c>
+      <c r="T61" s="140">
+        <v>8</v>
+      </c>
+      <c r="U61" s="140">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="V61" s="95">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A62" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62">
+        <v>2111</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>21</v>
+      </c>
+      <c r="E62">
+        <v>12</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="G62" s="95">
+        <f t="shared" si="7"/>
+        <v>57.142857142857139</v>
+      </c>
+      <c r="P62" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q62" s="140">
+        <f t="shared" si="5"/>
+        <v>3358601</v>
+      </c>
+      <c r="R62" s="140">
+        <v>1</v>
+      </c>
+      <c r="S62" s="140">
+        <v>21</v>
+      </c>
+      <c r="T62" s="140">
+        <v>12</v>
+      </c>
+      <c r="U62" s="140">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="V62" s="95">
+        <f t="shared" si="9"/>
+        <v>57.142857142857139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A63" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63">
+        <v>2111</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>18</v>
+      </c>
+      <c r="E63">
+        <v>8</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="G63" s="95">
+        <f t="shared" si="7"/>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="P63" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q63" s="140">
+        <f t="shared" si="5"/>
+        <v>3358601</v>
+      </c>
+      <c r="R63" s="140">
+        <v>2</v>
+      </c>
+      <c r="S63" s="140">
+        <v>18</v>
+      </c>
+      <c r="T63" s="140">
+        <v>8</v>
+      </c>
+      <c r="U63" s="140">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="V63" s="95">
+        <f t="shared" si="9"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A64" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64">
+        <v>2111</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>21</v>
+      </c>
+      <c r="E64">
+        <v>9</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="G64" s="95">
+        <f t="shared" si="7"/>
+        <v>42.857142857142854</v>
+      </c>
+      <c r="P64" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q64" s="140">
+        <f t="shared" si="5"/>
+        <v>3358601</v>
+      </c>
+      <c r="R64" s="140">
+        <v>3</v>
+      </c>
+      <c r="S64" s="140">
+        <v>21</v>
+      </c>
+      <c r="T64" s="140">
+        <v>9</v>
+      </c>
+      <c r="U64" s="140">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="V64" s="95">
+        <f t="shared" si="9"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A65" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>23</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+      <c r="F65">
+        <f>D65-E65</f>
+        <v>18</v>
+      </c>
+      <c r="G65" s="95">
+        <f>E65/D65*100</f>
+        <v>21.739130434782609</v>
+      </c>
+      <c r="P65" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q65" s="140">
+        <f>B65*863</f>
+        <v>0</v>
+      </c>
+      <c r="R65" s="140">
+        <v>1</v>
+      </c>
+      <c r="S65" s="140">
+        <v>23</v>
+      </c>
+      <c r="T65" s="140">
+        <v>5</v>
+      </c>
+      <c r="U65" s="140">
+        <f>S65-T65</f>
+        <v>18</v>
+      </c>
+      <c r="V65" s="95">
+        <f>T65/S65*100</f>
+        <v>21.739130434782609</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A66" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>18</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ref="F66:F97" si="10">D66-E66</f>
+        <v>14</v>
+      </c>
+      <c r="G66" s="95">
+        <f t="shared" ref="G66:G97" si="11">E66/D66*100</f>
+        <v>22.222222222222221</v>
+      </c>
+      <c r="P66" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q66" s="140">
+        <f t="shared" ref="Q66:Q97" si="12">B66*863</f>
+        <v>0</v>
+      </c>
+      <c r="R66" s="140">
+        <v>2</v>
+      </c>
+      <c r="S66" s="140">
+        <v>18</v>
+      </c>
+      <c r="T66" s="140">
+        <v>4</v>
+      </c>
+      <c r="U66" s="140">
+        <f t="shared" ref="U66:U97" si="13">S66-T66</f>
+        <v>14</v>
+      </c>
+      <c r="V66" s="95">
+        <f t="shared" ref="V66:V97" si="14">T66/S66*100</f>
+        <v>22.222222222222221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A67" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>30</v>
+      </c>
+      <c r="E67">
+        <v>9</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="10"/>
+        <v>21</v>
+      </c>
+      <c r="G67" s="95">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="P67" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q67" s="140">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R67" s="140">
+        <v>3</v>
+      </c>
+      <c r="S67" s="140">
+        <v>30</v>
+      </c>
+      <c r="T67" s="140">
+        <v>9</v>
+      </c>
+      <c r="U67" s="140">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="V67" s="95">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A68" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>17</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="G68" s="95">
+        <f t="shared" si="11"/>
+        <v>5.8823529411764701</v>
+      </c>
+      <c r="P68" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q68" s="140">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R68" s="140">
+        <v>4</v>
+      </c>
+      <c r="S68" s="140">
+        <v>17</v>
+      </c>
+      <c r="T68" s="140">
+        <v>1</v>
+      </c>
+      <c r="U68" s="140">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="V68" s="95">
+        <f t="shared" si="14"/>
+        <v>5.8823529411764701</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A69" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>27</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="G69" s="95">
+        <f t="shared" si="11"/>
+        <v>14.814814814814813</v>
+      </c>
+      <c r="P69" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q69" s="140">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R69" s="140">
+        <v>5</v>
+      </c>
+      <c r="S69" s="140">
+        <v>27</v>
+      </c>
+      <c r="T69" s="140">
+        <v>4</v>
+      </c>
+      <c r="U69" s="140">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="V69" s="95">
+        <f t="shared" si="14"/>
+        <v>14.814814814814813</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A70" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>6</v>
+      </c>
+      <c r="D70">
+        <v>18</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="G70" s="95">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P70" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q70" s="140">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R70" s="140">
+        <v>6</v>
+      </c>
+      <c r="S70" s="140">
+        <v>18</v>
+      </c>
+      <c r="T70" s="140">
+        <v>0</v>
+      </c>
+      <c r="U70" s="140">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="V70" s="95">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A71" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71">
+        <v>49</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>39</v>
+      </c>
+      <c r="E71">
+        <v>11</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="10"/>
+        <v>28</v>
+      </c>
+      <c r="G71" s="95">
+        <f t="shared" si="11"/>
+        <v>28.205128205128204</v>
+      </c>
+      <c r="P71" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q71" s="140">
+        <f t="shared" si="12"/>
+        <v>42287</v>
+      </c>
+      <c r="R71" s="140">
+        <v>1</v>
+      </c>
+      <c r="S71" s="140">
+        <v>39</v>
+      </c>
+      <c r="T71" s="140">
+        <v>11</v>
+      </c>
+      <c r="U71" s="140">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="V71" s="95">
+        <f t="shared" si="14"/>
+        <v>28.205128205128204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A72" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72">
+        <v>49</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>24</v>
+      </c>
+      <c r="E72">
+        <v>8</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="G72" s="95">
+        <f t="shared" si="11"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="P72" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q72" s="140">
+        <f t="shared" si="12"/>
+        <v>42287</v>
+      </c>
+      <c r="R72" s="140">
+        <v>2</v>
+      </c>
+      <c r="S72" s="140">
+        <v>24</v>
+      </c>
+      <c r="T72" s="140">
+        <v>8</v>
+      </c>
+      <c r="U72" s="140">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="V72" s="95">
+        <f t="shared" si="14"/>
+        <v>33.333333333333329</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A73" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73">
+        <v>49</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73">
+        <v>20</v>
+      </c>
+      <c r="E73">
+        <v>6</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="G73" s="95">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="P73" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q73" s="140">
+        <f t="shared" si="12"/>
+        <v>42287</v>
+      </c>
+      <c r="R73" s="140">
+        <v>3</v>
+      </c>
+      <c r="S73" s="140">
+        <v>20</v>
+      </c>
+      <c r="T73" s="140">
+        <v>6</v>
+      </c>
+      <c r="U73" s="140">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="V73" s="95">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A74" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74">
+        <v>77</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>28</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="10"/>
+        <v>22</v>
+      </c>
+      <c r="G74" s="95">
+        <f t="shared" si="11"/>
+        <v>21.428571428571427</v>
+      </c>
+      <c r="P74" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q74" s="140">
+        <f t="shared" si="12"/>
+        <v>66451</v>
+      </c>
+      <c r="R74" s="140">
+        <v>1</v>
+      </c>
+      <c r="S74" s="140">
+        <v>28</v>
+      </c>
+      <c r="T74" s="140">
+        <v>6</v>
+      </c>
+      <c r="U74" s="140">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="V74" s="95">
+        <f t="shared" si="14"/>
+        <v>21.428571428571427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A75" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75">
+        <v>77</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>20</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="G75" s="95">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="P75" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q75" s="140">
+        <f t="shared" si="12"/>
+        <v>66451</v>
+      </c>
+      <c r="R75" s="140">
+        <v>2</v>
+      </c>
+      <c r="S75" s="140">
+        <v>20</v>
+      </c>
+      <c r="T75" s="140">
+        <v>2</v>
+      </c>
+      <c r="U75" s="140">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="V75" s="95">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A76" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76">
+        <v>77</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>29</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="G76" s="95">
+        <f t="shared" si="11"/>
+        <v>13.793103448275861</v>
+      </c>
+      <c r="P76" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q76" s="140">
+        <f t="shared" si="12"/>
+        <v>66451</v>
+      </c>
+      <c r="R76" s="140">
+        <v>3</v>
+      </c>
+      <c r="S76" s="140">
+        <v>29</v>
+      </c>
+      <c r="T76" s="140">
+        <v>4</v>
+      </c>
+      <c r="U76" s="140">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="V76" s="95">
+        <f t="shared" si="14"/>
+        <v>13.793103448275861</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A77" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77">
+        <v>148</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>68</v>
+      </c>
+      <c r="E77">
+        <v>21</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="10"/>
+        <v>47</v>
+      </c>
+      <c r="G77" s="95">
+        <f t="shared" si="11"/>
+        <v>30.882352941176471</v>
+      </c>
+      <c r="P77" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q77" s="140">
+        <f t="shared" si="12"/>
+        <v>127724</v>
+      </c>
+      <c r="R77" s="140">
+        <v>1</v>
+      </c>
+      <c r="S77" s="140">
+        <v>68</v>
+      </c>
+      <c r="T77" s="140">
+        <v>21</v>
+      </c>
+      <c r="U77" s="140">
+        <f t="shared" si="13"/>
+        <v>47</v>
+      </c>
+      <c r="V77" s="95">
+        <f t="shared" si="14"/>
+        <v>30.882352941176471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A78" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78">
+        <v>148</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>41</v>
+      </c>
+      <c r="E78">
+        <v>12</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="10"/>
+        <v>29</v>
+      </c>
+      <c r="G78" s="95">
+        <f t="shared" si="11"/>
+        <v>29.268292682926827</v>
+      </c>
+      <c r="P78" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q78" s="140">
+        <f t="shared" si="12"/>
+        <v>127724</v>
+      </c>
+      <c r="R78" s="140">
+        <v>2</v>
+      </c>
+      <c r="S78" s="140">
+        <v>41</v>
+      </c>
+      <c r="T78" s="140">
+        <v>12</v>
+      </c>
+      <c r="U78" s="140">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="V78" s="95">
+        <f t="shared" si="14"/>
+        <v>29.268292682926827</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A79" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79">
+        <v>148</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>17</v>
+      </c>
+      <c r="E79">
+        <v>7</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="G79" s="95">
+        <f t="shared" si="11"/>
+        <v>41.17647058823529</v>
+      </c>
+      <c r="P79" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q79" s="140">
+        <f t="shared" si="12"/>
+        <v>127724</v>
+      </c>
+      <c r="R79" s="140">
+        <v>3</v>
+      </c>
+      <c r="S79" s="140">
+        <v>17</v>
+      </c>
+      <c r="T79" s="140">
+        <v>7</v>
+      </c>
+      <c r="U79" s="140">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="V79" s="95">
+        <f t="shared" si="14"/>
+        <v>41.17647058823529</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A80" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80">
+        <v>231</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>14</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="G80" s="95">
+        <f t="shared" si="11"/>
+        <v>28.571428571428569</v>
+      </c>
+      <c r="P80" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q80" s="140">
+        <f t="shared" si="12"/>
+        <v>199353</v>
+      </c>
+      <c r="R80" s="140">
+        <v>1</v>
+      </c>
+      <c r="S80" s="140">
+        <v>14</v>
+      </c>
+      <c r="T80" s="140">
+        <v>4</v>
+      </c>
+      <c r="U80" s="140">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="V80" s="95">
+        <f t="shared" si="14"/>
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A81" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81">
+        <v>231</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>21</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="G81" s="95">
+        <f t="shared" si="11"/>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="P81" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q81" s="140">
+        <f t="shared" si="12"/>
+        <v>199353</v>
+      </c>
+      <c r="R81" s="140">
+        <v>2</v>
+      </c>
+      <c r="S81" s="140">
+        <v>21</v>
+      </c>
+      <c r="T81" s="140">
+        <v>3</v>
+      </c>
+      <c r="U81" s="140">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="V81" s="95">
+        <f t="shared" si="14"/>
+        <v>14.285714285714285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A82" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82">
+        <v>231</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <v>39</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="10"/>
+        <v>34</v>
+      </c>
+      <c r="G82" s="95">
+        <f t="shared" si="11"/>
+        <v>12.820512820512819</v>
+      </c>
+      <c r="P82" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q82" s="140">
+        <f t="shared" si="12"/>
+        <v>199353</v>
+      </c>
+      <c r="R82" s="140">
+        <v>3</v>
+      </c>
+      <c r="S82" s="140">
+        <v>39</v>
+      </c>
+      <c r="T82" s="140">
+        <v>5</v>
+      </c>
+      <c r="U82" s="140">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
+      <c r="V82" s="95">
+        <f t="shared" si="14"/>
+        <v>12.820512820512819</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A83" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B83">
+        <v>444</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>82</v>
+      </c>
+      <c r="E83">
+        <v>24</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="10"/>
+        <v>58</v>
+      </c>
+      <c r="G83" s="95">
+        <f t="shared" si="11"/>
+        <v>29.268292682926827</v>
+      </c>
+      <c r="P83" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q83" s="140">
+        <f t="shared" si="12"/>
+        <v>383172</v>
+      </c>
+      <c r="R83" s="140">
+        <v>1</v>
+      </c>
+      <c r="S83" s="140">
+        <v>82</v>
+      </c>
+      <c r="T83" s="140">
+        <v>24</v>
+      </c>
+      <c r="U83" s="140">
+        <f t="shared" si="13"/>
+        <v>58</v>
+      </c>
+      <c r="V83" s="95">
+        <f t="shared" si="14"/>
+        <v>29.268292682926827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A84" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B84">
+        <v>444</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84">
+        <v>25</v>
+      </c>
+      <c r="E84">
+        <v>8</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="G84" s="95">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="P84" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q84" s="140">
+        <f t="shared" si="12"/>
+        <v>383172</v>
+      </c>
+      <c r="R84" s="140">
+        <v>2</v>
+      </c>
+      <c r="S84" s="140">
+        <v>25</v>
+      </c>
+      <c r="T84" s="140">
+        <v>8</v>
+      </c>
+      <c r="U84" s="140">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="V84" s="95">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A85" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B85">
+        <v>444</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85">
+        <v>55</v>
+      </c>
+      <c r="E85">
+        <v>12</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="10"/>
+        <v>43</v>
+      </c>
+      <c r="G85" s="95">
+        <f t="shared" si="11"/>
+        <v>21.818181818181817</v>
+      </c>
+      <c r="P85" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q85" s="140">
+        <f t="shared" si="12"/>
+        <v>383172</v>
+      </c>
+      <c r="R85" s="140">
+        <v>3</v>
+      </c>
+      <c r="S85" s="140">
+        <v>55</v>
+      </c>
+      <c r="T85" s="140">
+        <v>12</v>
+      </c>
+      <c r="U85" s="140">
+        <f t="shared" si="13"/>
+        <v>43</v>
+      </c>
+      <c r="V85" s="95">
+        <f t="shared" si="14"/>
+        <v>21.818181818181817</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A86" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86">
+        <v>694</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>17</v>
+      </c>
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="G86" s="95">
+        <f t="shared" si="11"/>
+        <v>29.411764705882355</v>
+      </c>
+      <c r="P86" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q86" s="140">
+        <f t="shared" si="12"/>
+        <v>598922</v>
+      </c>
+      <c r="R86" s="140">
+        <v>1</v>
+      </c>
+      <c r="S86" s="140">
+        <v>17</v>
+      </c>
+      <c r="T86" s="140">
+        <v>5</v>
+      </c>
+      <c r="U86" s="140">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="V86" s="95">
+        <f t="shared" si="14"/>
+        <v>29.411764705882355</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A87" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87">
+        <v>694</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>22</v>
+      </c>
+      <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="G87" s="95">
+        <f t="shared" si="11"/>
+        <v>18.181818181818183</v>
+      </c>
+      <c r="P87" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q87" s="140">
+        <f t="shared" si="12"/>
+        <v>598922</v>
+      </c>
+      <c r="R87" s="140">
+        <v>2</v>
+      </c>
+      <c r="S87" s="140">
+        <v>22</v>
+      </c>
+      <c r="T87" s="140">
+        <v>4</v>
+      </c>
+      <c r="U87" s="140">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="V87" s="95">
+        <f t="shared" si="14"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A88" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B88">
+        <v>694</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88">
+        <v>15</v>
+      </c>
+      <c r="E88">
+        <v>4</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="G88" s="95">
+        <f t="shared" si="11"/>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="P88" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q88" s="140">
+        <f t="shared" si="12"/>
+        <v>598922</v>
+      </c>
+      <c r="R88" s="140">
+        <v>3</v>
+      </c>
+      <c r="S88" s="140">
+        <v>15</v>
+      </c>
+      <c r="T88" s="140">
+        <v>4</v>
+      </c>
+      <c r="U88" s="140">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="V88" s="95">
+        <f t="shared" si="14"/>
+        <v>26.666666666666668</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A89" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89">
+        <v>1333</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>21</v>
+      </c>
+      <c r="E89">
+        <v>8</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="G89" s="95">
+        <f t="shared" si="11"/>
+        <v>38.095238095238095</v>
+      </c>
+      <c r="P89" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q89" s="140">
+        <f t="shared" si="12"/>
+        <v>1150379</v>
+      </c>
+      <c r="R89" s="140">
+        <v>1</v>
+      </c>
+      <c r="S89" s="140">
+        <v>21</v>
+      </c>
+      <c r="T89" s="140">
+        <v>8</v>
+      </c>
+      <c r="U89" s="140">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="V89" s="95">
+        <f t="shared" si="14"/>
+        <v>38.095238095238095</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A90" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B90">
+        <v>1333</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>27</v>
+      </c>
+      <c r="E90">
+        <v>8</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="G90" s="95">
+        <f t="shared" si="11"/>
+        <v>29.629629629629626</v>
+      </c>
+      <c r="P90" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q90" s="140">
+        <f t="shared" si="12"/>
+        <v>1150379</v>
+      </c>
+      <c r="R90" s="140">
+        <v>2</v>
+      </c>
+      <c r="S90" s="140">
+        <v>27</v>
+      </c>
+      <c r="T90" s="140">
+        <v>8</v>
+      </c>
+      <c r="U90" s="140">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="V90" s="95">
+        <f t="shared" si="14"/>
+        <v>29.629629629629626</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A91" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B91">
+        <v>1333</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91">
+        <v>37</v>
+      </c>
+      <c r="E91">
+        <v>13</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="G91" s="95">
+        <f t="shared" si="11"/>
+        <v>35.135135135135137</v>
+      </c>
+      <c r="P91" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q91" s="140">
+        <f t="shared" si="12"/>
+        <v>1150379</v>
+      </c>
+      <c r="R91" s="140">
+        <v>3</v>
+      </c>
+      <c r="S91" s="140">
+        <v>37</v>
+      </c>
+      <c r="T91" s="140">
+        <v>13</v>
+      </c>
+      <c r="U91" s="140">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="V91" s="95">
+        <f t="shared" si="14"/>
+        <v>35.135135135135137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A92" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92">
+        <v>2083</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>14</v>
+      </c>
+      <c r="E92">
+        <v>6</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="G92" s="95">
+        <f t="shared" si="11"/>
+        <v>42.857142857142854</v>
+      </c>
+      <c r="P92" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q92" s="140">
+        <f t="shared" si="12"/>
+        <v>1797629</v>
+      </c>
+      <c r="R92" s="140">
+        <v>1</v>
+      </c>
+      <c r="S92" s="140">
+        <v>14</v>
+      </c>
+      <c r="T92" s="140">
+        <v>6</v>
+      </c>
+      <c r="U92" s="140">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="V92" s="95">
+        <f t="shared" si="14"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A93" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B93">
+        <v>2083</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>31</v>
+      </c>
+      <c r="E93">
+        <v>9</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="10"/>
+        <v>22</v>
+      </c>
+      <c r="G93" s="95">
+        <f t="shared" si="11"/>
+        <v>29.032258064516132</v>
+      </c>
+      <c r="P93" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q93" s="140">
+        <f t="shared" si="12"/>
+        <v>1797629</v>
+      </c>
+      <c r="R93" s="140">
+        <v>2</v>
+      </c>
+      <c r="S93" s="140">
+        <v>31</v>
+      </c>
+      <c r="T93" s="140">
+        <v>9</v>
+      </c>
+      <c r="U93" s="140">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="V93" s="95">
+        <f t="shared" si="14"/>
+        <v>29.032258064516132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A94" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94">
+        <v>2083</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>71</v>
+      </c>
+      <c r="E94">
+        <v>12</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="10"/>
+        <v>59</v>
+      </c>
+      <c r="G94" s="95">
+        <f t="shared" si="11"/>
+        <v>16.901408450704224</v>
+      </c>
+      <c r="P94" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q94" s="140">
+        <f t="shared" si="12"/>
+        <v>1797629</v>
+      </c>
+      <c r="R94" s="140">
+        <v>3</v>
+      </c>
+      <c r="S94" s="140">
+        <v>71</v>
+      </c>
+      <c r="T94" s="140">
+        <v>12</v>
+      </c>
+      <c r="U94" s="140">
+        <f t="shared" si="13"/>
+        <v>59</v>
+      </c>
+      <c r="V94" s="95">
+        <f t="shared" si="14"/>
+        <v>16.901408450704224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A95" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B95">
+        <v>4000</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>19</v>
+      </c>
+      <c r="E95">
+        <v>8</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="G95" s="95">
+        <f t="shared" si="11"/>
+        <v>42.105263157894733</v>
+      </c>
+      <c r="P95" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q95" s="140">
+        <f t="shared" si="12"/>
+        <v>3452000</v>
+      </c>
+      <c r="R95" s="140">
+        <v>1</v>
+      </c>
+      <c r="S95" s="140">
+        <v>19</v>
+      </c>
+      <c r="T95" s="140">
+        <v>8</v>
+      </c>
+      <c r="U95" s="140">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="V95" s="95">
+        <f t="shared" si="14"/>
+        <v>42.105263157894733</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A96" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="B96">
+        <v>4000</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96">
+        <v>43</v>
+      </c>
+      <c r="E96">
+        <v>11</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="G96" s="95">
+        <f t="shared" si="11"/>
+        <v>25.581395348837212</v>
+      </c>
+      <c r="P96" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q96" s="140">
+        <f t="shared" si="12"/>
+        <v>3452000</v>
+      </c>
+      <c r="R96" s="140">
+        <v>2</v>
+      </c>
+      <c r="S96" s="140">
+        <v>43</v>
+      </c>
+      <c r="T96" s="140">
+        <v>11</v>
+      </c>
+      <c r="U96" s="140">
+        <f t="shared" si="13"/>
+        <v>32</v>
+      </c>
+      <c r="V96" s="95">
+        <f t="shared" si="14"/>
+        <v>25.581395348837212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" s="97">
+        <v>4000</v>
+      </c>
+      <c r="C97" s="97">
+        <v>3</v>
+      </c>
+      <c r="D97" s="97">
+        <v>36</v>
+      </c>
+      <c r="E97" s="97">
+        <v>11</v>
+      </c>
+      <c r="F97" s="97">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="G97" s="98">
+        <f t="shared" si="11"/>
+        <v>30.555555555555557</v>
+      </c>
+      <c r="P97" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q97" s="97">
+        <f t="shared" si="12"/>
+        <v>3452000</v>
+      </c>
+      <c r="R97" s="97">
+        <v>3</v>
+      </c>
+      <c r="S97" s="97">
+        <v>36</v>
+      </c>
+      <c r="T97" s="97">
+        <v>11</v>
+      </c>
+      <c r="U97" s="97">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="V97" s="98">
+        <f t="shared" si="14"/>
+        <v>30.555555555555557</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7740F7CB-B022-D54A-8B3D-A142666DC5C9}">
+  <dimension ref="A1:H97"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="141" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="142" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="142" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="142" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="140">
+        <v>0</v>
+      </c>
+      <c r="C2" s="140">
+        <v>0</v>
+      </c>
+      <c r="D2" s="140">
+        <v>1</v>
+      </c>
+      <c r="E2" s="140">
+        <v>20</v>
+      </c>
+      <c r="F2" s="140">
+        <v>7</v>
+      </c>
+      <c r="G2" s="140">
+        <f>E2-F2</f>
+        <v>13</v>
+      </c>
+      <c r="H2" s="140">
+        <f>F2/E2*100</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="140">
+        <v>0</v>
+      </c>
+      <c r="C3" s="140">
+        <v>0</v>
+      </c>
+      <c r="D3" s="140">
+        <v>2</v>
+      </c>
+      <c r="E3" s="140">
+        <v>33</v>
+      </c>
+      <c r="F3" s="140">
+        <v>8</v>
+      </c>
+      <c r="G3" s="140">
+        <f t="shared" ref="G3:G34" si="0">E3-F3</f>
+        <v>25</v>
+      </c>
+      <c r="H3" s="140">
+        <f t="shared" ref="H3:H34" si="1">F3/E3*100</f>
+        <v>24.242424242424242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="140">
+        <v>0</v>
+      </c>
+      <c r="C4" s="140">
+        <v>0</v>
+      </c>
+      <c r="D4" s="140">
+        <v>3</v>
+      </c>
+      <c r="E4" s="140">
+        <v>32</v>
+      </c>
+      <c r="F4" s="140">
+        <v>5</v>
+      </c>
+      <c r="G4" s="140">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H4" s="140">
+        <f t="shared" si="1"/>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="140">
+        <v>0</v>
+      </c>
+      <c r="C5" s="140">
+        <v>0</v>
+      </c>
+      <c r="D5" s="140">
+        <v>4</v>
+      </c>
+      <c r="E5" s="140">
+        <v>30</v>
+      </c>
+      <c r="F5" s="140">
+        <v>2</v>
+      </c>
+      <c r="G5" s="140">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="H5" s="140">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="140">
+        <v>0</v>
+      </c>
+      <c r="C6" s="140">
+        <v>0</v>
+      </c>
+      <c r="D6" s="140">
+        <v>5</v>
+      </c>
+      <c r="E6" s="140">
+        <v>35</v>
+      </c>
+      <c r="F6" s="140">
+        <v>8</v>
+      </c>
+      <c r="G6" s="140">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H6" s="140">
+        <f t="shared" si="1"/>
+        <v>22.857142857142858</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="140">
+        <v>0</v>
+      </c>
+      <c r="C7" s="140">
+        <v>0</v>
+      </c>
+      <c r="D7" s="140">
+        <v>6</v>
+      </c>
+      <c r="E7" s="140">
+        <v>35</v>
+      </c>
+      <c r="F7" s="140">
+        <v>7</v>
+      </c>
+      <c r="G7" s="140">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="H7" s="140">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="140">
+        <v>76187.5</v>
+      </c>
+      <c r="C8" s="140">
+        <v>0.53</v>
+      </c>
+      <c r="D8" s="140">
+        <v>1</v>
+      </c>
+      <c r="E8" s="140">
+        <v>25</v>
+      </c>
+      <c r="F8" s="140">
+        <v>6</v>
+      </c>
+      <c r="G8" s="140">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H8" s="140">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="140">
+        <v>76187.5</v>
+      </c>
+      <c r="C9" s="140">
+        <v>0.53</v>
+      </c>
+      <c r="D9" s="140">
+        <v>2</v>
+      </c>
+      <c r="E9" s="140">
+        <v>21</v>
+      </c>
+      <c r="F9" s="140">
+        <v>4</v>
+      </c>
+      <c r="G9" s="140">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H9" s="140">
+        <f t="shared" si="1"/>
+        <v>19.047619047619047</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="140">
+        <v>76187.5</v>
+      </c>
+      <c r="C10" s="140">
+        <v>0.53</v>
+      </c>
+      <c r="D10" s="140">
+        <v>3</v>
+      </c>
+      <c r="E10" s="140">
+        <v>41</v>
+      </c>
+      <c r="F10" s="140">
+        <v>10</v>
+      </c>
+      <c r="G10" s="140">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="H10" s="140">
+        <f t="shared" si="1"/>
+        <v>24.390243902439025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="140">
+        <v>230000</v>
+      </c>
+      <c r="C11" s="140">
+        <v>1.6</v>
+      </c>
+      <c r="D11" s="140">
+        <v>1</v>
+      </c>
+      <c r="E11" s="140">
+        <v>27</v>
+      </c>
+      <c r="F11" s="140">
+        <v>8</v>
+      </c>
+      <c r="G11" s="140">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H11" s="140">
+        <f t="shared" si="1"/>
+        <v>29.629629629629626</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="140">
+        <v>230000</v>
+      </c>
+      <c r="C12" s="140">
+        <v>1.6</v>
+      </c>
+      <c r="D12" s="140">
+        <v>2</v>
+      </c>
+      <c r="E12" s="140">
+        <v>24</v>
+      </c>
+      <c r="F12" s="140">
+        <v>7</v>
+      </c>
+      <c r="G12" s="140">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H12" s="140">
+        <f t="shared" si="1"/>
+        <v>29.166666666666668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="140">
+        <v>230000</v>
+      </c>
+      <c r="C13" s="140">
+        <v>1.6</v>
+      </c>
+      <c r="D13" s="140">
+        <v>3</v>
+      </c>
+      <c r="E13" s="140">
+        <v>38</v>
+      </c>
+      <c r="F13" s="140">
+        <v>12</v>
+      </c>
+      <c r="G13" s="140">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="H13" s="140">
+        <f t="shared" si="1"/>
+        <v>31.578947368421051</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="140">
+        <v>632500</v>
+      </c>
+      <c r="C14" s="140">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D14" s="140">
+        <v>1</v>
+      </c>
+      <c r="E14" s="140">
+        <v>24</v>
+      </c>
+      <c r="F14" s="140">
+        <v>6</v>
+      </c>
+      <c r="G14" s="140">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H14" s="140">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="140">
+        <v>632500</v>
+      </c>
+      <c r="C15" s="140">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D15" s="140">
+        <v>2</v>
+      </c>
+      <c r="E15" s="140">
+        <v>62</v>
+      </c>
+      <c r="F15" s="140">
+        <v>26</v>
+      </c>
+      <c r="G15" s="140">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="H15" s="140">
+        <f t="shared" si="1"/>
+        <v>41.935483870967744</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="140">
+        <v>632500</v>
+      </c>
+      <c r="C16" s="140">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D16" s="140">
+        <v>3</v>
+      </c>
+      <c r="E16" s="140">
+        <v>28</v>
+      </c>
+      <c r="F16" s="140">
+        <v>8</v>
+      </c>
+      <c r="G16" s="140">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H16" s="140">
+        <f t="shared" si="1"/>
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="140">
+        <v>675625</v>
+      </c>
+      <c r="C17" s="140">
+        <v>4.7</v>
+      </c>
+      <c r="D17" s="140">
+        <v>1</v>
+      </c>
+      <c r="E17" s="140">
+        <v>21</v>
+      </c>
+      <c r="F17" s="140">
+        <v>9</v>
+      </c>
+      <c r="G17" s="140">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="H17" s="140">
+        <f t="shared" si="1"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="140">
+        <v>675625</v>
+      </c>
+      <c r="C18" s="140">
+        <v>4.7</v>
+      </c>
+      <c r="D18" s="140">
+        <v>2</v>
+      </c>
+      <c r="E18" s="140">
+        <v>57</v>
+      </c>
+      <c r="F18" s="140">
+        <v>15</v>
+      </c>
+      <c r="G18" s="140">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="H18" s="140">
+        <f t="shared" si="1"/>
+        <v>26.315789473684209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="140">
+        <v>675625</v>
+      </c>
+      <c r="C19" s="140">
+        <v>4.7</v>
+      </c>
+      <c r="D19" s="140">
+        <v>3</v>
+      </c>
+      <c r="E19" s="140">
+        <v>67</v>
+      </c>
+      <c r="F19" s="140">
+        <v>19</v>
+      </c>
+      <c r="G19" s="140">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="H19" s="140">
+        <f t="shared" si="1"/>
+        <v>28.35820895522388</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="140">
+        <v>1868750</v>
+      </c>
+      <c r="C20" s="140">
+        <v>13</v>
+      </c>
+      <c r="D20" s="140">
+        <v>1</v>
+      </c>
+      <c r="E20" s="140">
+        <v>15</v>
+      </c>
+      <c r="F20" s="140">
+        <v>5</v>
+      </c>
+      <c r="G20" s="140">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H20" s="140">
+        <f t="shared" si="1"/>
+        <v>33.333333333333329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="140">
+        <v>1868750</v>
+      </c>
+      <c r="C21" s="140">
+        <v>13</v>
+      </c>
+      <c r="D21" s="140">
+        <v>2</v>
+      </c>
+      <c r="E21" s="140">
+        <v>43</v>
+      </c>
+      <c r="F21" s="140">
+        <v>16</v>
+      </c>
+      <c r="G21" s="140">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H21" s="140">
+        <f t="shared" si="1"/>
+        <v>37.209302325581397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="140">
+        <v>1868750</v>
+      </c>
+      <c r="C22" s="140">
+        <v>13</v>
+      </c>
+      <c r="D22" s="140">
+        <v>3</v>
+      </c>
+      <c r="E22" s="140">
+        <v>64</v>
+      </c>
+      <c r="F22" s="140">
+        <v>20</v>
+      </c>
+      <c r="G22" s="140">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="H22" s="140">
+        <f t="shared" si="1"/>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="140">
+        <v>2012500</v>
+      </c>
+      <c r="C23" s="140">
+        <v>14</v>
+      </c>
+      <c r="D23" s="140">
+        <v>1</v>
+      </c>
+      <c r="E23" s="140">
+        <v>13</v>
+      </c>
+      <c r="F23" s="140">
+        <v>6</v>
+      </c>
+      <c r="G23" s="140">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H23" s="140">
+        <f t="shared" si="1"/>
+        <v>46.153846153846153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="140">
+        <v>2012500</v>
+      </c>
+      <c r="C24" s="140">
+        <v>14</v>
+      </c>
+      <c r="D24" s="140">
+        <v>2</v>
+      </c>
+      <c r="E24" s="140">
+        <v>50</v>
+      </c>
+      <c r="F24" s="140">
+        <v>17</v>
+      </c>
+      <c r="G24" s="140">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H24" s="140">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="140">
+        <v>2012500</v>
+      </c>
+      <c r="C25" s="140">
+        <v>14</v>
+      </c>
+      <c r="D25" s="140">
+        <v>3</v>
+      </c>
+      <c r="E25" s="140">
+        <v>49</v>
+      </c>
+      <c r="F25" s="140">
+        <v>18</v>
+      </c>
+      <c r="G25" s="140">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="H25" s="140">
+        <f t="shared" si="1"/>
+        <v>36.734693877551024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="140">
+        <v>5750000</v>
+      </c>
+      <c r="C26" s="140">
+        <v>40</v>
+      </c>
+      <c r="D26" s="140">
+        <v>1</v>
+      </c>
+      <c r="E26" s="140">
+        <v>21</v>
+      </c>
+      <c r="F26" s="140">
+        <v>8</v>
+      </c>
+      <c r="G26" s="140">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H26" s="140">
+        <f t="shared" si="1"/>
+        <v>38.095238095238095</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="140">
+        <v>5750000</v>
+      </c>
+      <c r="C27" s="140">
+        <v>40</v>
+      </c>
+      <c r="D27" s="140">
+        <v>2</v>
+      </c>
+      <c r="E27" s="140">
+        <v>54</v>
+      </c>
+      <c r="F27" s="140">
+        <v>21</v>
+      </c>
+      <c r="G27" s="140">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H27" s="140">
+        <f t="shared" si="1"/>
+        <v>38.888888888888893</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="140">
+        <v>5750000</v>
+      </c>
+      <c r="C28" s="140">
+        <v>40</v>
+      </c>
+      <c r="D28" s="140">
+        <v>3</v>
+      </c>
+      <c r="E28" s="140">
+        <v>59</v>
+      </c>
+      <c r="F28" s="140">
+        <v>22</v>
+      </c>
+      <c r="G28" s="140">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="H28" s="140">
+        <f t="shared" si="1"/>
+        <v>37.288135593220339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="140">
+        <v>6181250</v>
+      </c>
+      <c r="C29" s="140">
+        <v>43</v>
+      </c>
+      <c r="D29" s="140">
+        <v>1</v>
+      </c>
+      <c r="E29" s="140">
+        <v>11</v>
+      </c>
+      <c r="F29" s="140">
+        <v>7</v>
+      </c>
+      <c r="G29" s="140">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H29" s="140">
+        <f t="shared" si="1"/>
+        <v>63.636363636363633</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="140">
+        <v>6181250</v>
+      </c>
+      <c r="C30" s="140">
+        <v>43</v>
+      </c>
+      <c r="D30" s="140">
+        <v>2</v>
+      </c>
+      <c r="E30" s="140">
+        <v>46</v>
+      </c>
+      <c r="F30" s="140">
+        <v>16</v>
+      </c>
+      <c r="G30" s="140">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H30" s="140">
+        <f t="shared" si="1"/>
+        <v>34.782608695652172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="140">
+        <v>6181250</v>
+      </c>
+      <c r="C31" s="140">
+        <v>43</v>
+      </c>
+      <c r="D31" s="140">
+        <v>3</v>
+      </c>
+      <c r="E31" s="140">
+        <v>19</v>
+      </c>
+      <c r="F31" s="140">
+        <v>7</v>
+      </c>
+      <c r="G31" s="140">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="H31" s="140">
+        <f t="shared" si="1"/>
+        <v>36.84210526315789</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="140">
+        <v>17250000</v>
+      </c>
+      <c r="C32" s="140">
+        <v>120</v>
+      </c>
+      <c r="D32" s="140">
+        <v>1</v>
+      </c>
+      <c r="E32" s="140">
+        <v>22</v>
+      </c>
+      <c r="F32" s="140">
+        <v>10</v>
+      </c>
+      <c r="G32" s="140">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="H32" s="140">
+        <f t="shared" si="1"/>
+        <v>45.454545454545453</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="140">
+        <v>17250000</v>
+      </c>
+      <c r="C33" s="140">
+        <v>120</v>
+      </c>
+      <c r="D33" s="140">
+        <v>2</v>
+      </c>
+      <c r="E33" s="140">
+        <v>38</v>
+      </c>
+      <c r="F33" s="140">
+        <v>12</v>
+      </c>
+      <c r="G33" s="140">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="H33" s="140">
+        <f t="shared" si="1"/>
+        <v>31.578947368421051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="140">
+        <v>17250000</v>
+      </c>
+      <c r="C34" s="140">
+        <v>120</v>
+      </c>
+      <c r="D34" s="140">
+        <v>3</v>
+      </c>
+      <c r="E34" s="140">
+        <v>40</v>
+      </c>
+      <c r="F34" s="140">
+        <v>14</v>
+      </c>
+      <c r="G34" s="140">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="H34" s="140">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="140">
+        <v>0</v>
+      </c>
+      <c r="C35" s="140">
+        <v>0</v>
+      </c>
+      <c r="D35" s="140">
+        <v>1</v>
+      </c>
+      <c r="E35" s="140">
+        <v>23</v>
+      </c>
+      <c r="F35" s="140">
+        <v>13</v>
+      </c>
+      <c r="G35" s="140">
+        <f>E35-F35</f>
+        <v>10</v>
+      </c>
+      <c r="H35" s="140">
+        <f>F35/E35*100</f>
+        <v>56.521739130434781</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="140">
+        <v>0</v>
+      </c>
+      <c r="C36" s="140">
+        <v>0</v>
+      </c>
+      <c r="D36" s="140">
+        <v>2</v>
+      </c>
+      <c r="E36" s="140">
+        <v>34</v>
+      </c>
+      <c r="F36" s="140">
+        <v>12</v>
+      </c>
+      <c r="G36" s="140">
+        <f>E36-F36</f>
+        <v>22</v>
+      </c>
+      <c r="H36" s="140">
+        <f>F36/E36*100</f>
+        <v>35.294117647058826</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="140">
+        <v>0</v>
+      </c>
+      <c r="C37" s="140">
+        <v>0</v>
+      </c>
+      <c r="D37" s="140">
+        <v>3</v>
+      </c>
+      <c r="E37" s="140">
+        <v>18</v>
+      </c>
+      <c r="F37" s="140">
+        <v>7</v>
+      </c>
+      <c r="G37" s="140">
+        <f t="shared" ref="G37:G64" si="2">E37-F37</f>
+        <v>11</v>
+      </c>
+      <c r="H37" s="140">
+        <f t="shared" ref="H37:H64" si="3">F37/E37*100</f>
+        <v>38.888888888888893</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="140">
+        <v>0</v>
+      </c>
+      <c r="C38" s="140">
+        <v>0</v>
+      </c>
+      <c r="D38" s="140">
+        <v>4</v>
+      </c>
+      <c r="E38" s="140">
+        <v>22</v>
+      </c>
+      <c r="F38" s="140">
+        <v>4</v>
+      </c>
+      <c r="G38" s="140">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="H38" s="140">
+        <f t="shared" si="3"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="140">
+        <v>0</v>
+      </c>
+      <c r="C39" s="140">
+        <v>0</v>
+      </c>
+      <c r="D39" s="140">
+        <v>5</v>
+      </c>
+      <c r="E39" s="140">
+        <v>22</v>
+      </c>
+      <c r="F39" s="140">
+        <v>4</v>
+      </c>
+      <c r="G39" s="140">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="H39" s="140">
+        <f t="shared" si="3"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="140">
+        <v>0</v>
+      </c>
+      <c r="C40" s="140">
+        <v>0</v>
+      </c>
+      <c r="D40" s="140">
+        <v>6</v>
+      </c>
+      <c r="E40" s="140">
+        <v>20</v>
+      </c>
+      <c r="F40" s="140">
+        <v>4</v>
+      </c>
+      <c r="G40" s="140">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H40" s="140">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="140">
+        <v>120916</v>
+      </c>
+      <c r="C41" s="140">
+        <v>76</v>
+      </c>
+      <c r="D41" s="140">
+        <v>1</v>
+      </c>
+      <c r="E41" s="140">
+        <v>23</v>
+      </c>
+      <c r="F41" s="140">
+        <v>7</v>
+      </c>
+      <c r="G41" s="140">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H41" s="140">
+        <f t="shared" si="3"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="140">
+        <v>120916</v>
+      </c>
+      <c r="C42" s="140">
+        <v>76</v>
+      </c>
+      <c r="D42" s="140">
+        <v>2</v>
+      </c>
+      <c r="E42" s="140">
+        <v>22</v>
+      </c>
+      <c r="F42" s="140">
+        <v>11</v>
+      </c>
+      <c r="G42" s="140">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="H42" s="140">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="140">
+        <v>120916</v>
+      </c>
+      <c r="C43" s="140">
+        <v>76</v>
+      </c>
+      <c r="D43" s="140">
+        <v>3</v>
+      </c>
+      <c r="E43" s="140">
+        <v>23</v>
+      </c>
+      <c r="F43" s="140">
+        <v>7</v>
+      </c>
+      <c r="G43" s="140">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H43" s="140">
+        <f t="shared" si="3"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="140">
+        <v>124098</v>
+      </c>
+      <c r="C44" s="140">
+        <v>78</v>
+      </c>
+      <c r="D44" s="140">
+        <v>1</v>
+      </c>
+      <c r="E44" s="140">
+        <v>19</v>
+      </c>
+      <c r="F44" s="140">
+        <v>4</v>
+      </c>
+      <c r="G44" s="140">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H44" s="140">
+        <f t="shared" si="3"/>
+        <v>21.052631578947366</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="140">
+        <v>124098</v>
+      </c>
+      <c r="C45" s="140">
+        <v>78</v>
+      </c>
+      <c r="D45" s="140">
+        <v>2</v>
+      </c>
+      <c r="E45" s="140">
+        <v>16</v>
+      </c>
+      <c r="F45" s="140">
+        <v>4</v>
+      </c>
+      <c r="G45" s="140">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="H45" s="140">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="140">
+        <v>124098</v>
+      </c>
+      <c r="C46" s="140">
+        <v>78</v>
+      </c>
+      <c r="D46" s="140">
+        <v>3</v>
+      </c>
+      <c r="E46" s="140">
+        <v>23</v>
+      </c>
+      <c r="F46" s="140">
+        <v>7</v>
+      </c>
+      <c r="G46" s="140">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H46" s="140">
+        <f t="shared" si="3"/>
+        <v>30.434782608695656</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="140">
+        <v>361157</v>
+      </c>
+      <c r="C47" s="140">
+        <v>227</v>
+      </c>
+      <c r="D47" s="140">
+        <v>1</v>
+      </c>
+      <c r="E47" s="140">
+        <v>10</v>
+      </c>
+      <c r="F47" s="140">
+        <v>4</v>
+      </c>
+      <c r="G47" s="140">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="H47" s="140">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="140">
+        <v>361157</v>
+      </c>
+      <c r="C48" s="140">
+        <v>227</v>
+      </c>
+      <c r="D48" s="140">
+        <v>2</v>
+      </c>
+      <c r="E48" s="140">
+        <v>26</v>
+      </c>
+      <c r="F48" s="140">
+        <v>11</v>
+      </c>
+      <c r="G48" s="140">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H48" s="140">
+        <f t="shared" si="3"/>
+        <v>42.307692307692307</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="140">
+        <v>361157</v>
+      </c>
+      <c r="C49" s="140">
+        <v>227</v>
+      </c>
+      <c r="D49" s="140">
+        <v>3</v>
+      </c>
+      <c r="E49" s="140">
+        <v>26</v>
+      </c>
+      <c r="F49" s="140">
+        <v>10</v>
+      </c>
+      <c r="G49" s="140">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="H49" s="140">
+        <f t="shared" si="3"/>
+        <v>38.461538461538467</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="140">
+        <v>373885</v>
+      </c>
+      <c r="C50" s="140">
+        <v>235</v>
+      </c>
+      <c r="D50" s="140">
+        <v>1</v>
+      </c>
+      <c r="E50" s="140">
+        <v>20</v>
+      </c>
+      <c r="F50" s="140">
+        <v>7</v>
+      </c>
+      <c r="G50" s="140">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H50" s="140">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="140">
+        <v>373885</v>
+      </c>
+      <c r="C51" s="140">
+        <v>235</v>
+      </c>
+      <c r="D51" s="140">
+        <v>2</v>
+      </c>
+      <c r="E51" s="140">
+        <v>22</v>
+      </c>
+      <c r="F51" s="140">
+        <v>7</v>
+      </c>
+      <c r="G51" s="140">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H51" s="140">
+        <f t="shared" si="3"/>
+        <v>31.818181818181817</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="140">
+        <v>373885</v>
+      </c>
+      <c r="C52" s="140">
+        <v>235</v>
+      </c>
+      <c r="D52" s="140">
+        <v>3</v>
+      </c>
+      <c r="E52" s="140">
+        <v>28</v>
+      </c>
+      <c r="F52" s="140">
+        <v>7</v>
+      </c>
+      <c r="G52" s="140">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="H52" s="140">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="140">
+        <v>1081880</v>
+      </c>
+      <c r="C53" s="140">
+        <v>680</v>
+      </c>
+      <c r="D53" s="140">
+        <v>1</v>
+      </c>
+      <c r="E53" s="140">
+        <v>37</v>
+      </c>
+      <c r="F53" s="140">
+        <v>20</v>
+      </c>
+      <c r="G53" s="140">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="H53" s="140">
+        <f t="shared" si="3"/>
+        <v>54.054054054054056</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="140">
+        <v>1081880</v>
+      </c>
+      <c r="C54" s="140">
+        <v>680</v>
+      </c>
+      <c r="D54" s="140">
+        <v>2</v>
+      </c>
+      <c r="E54" s="140">
+        <v>28</v>
+      </c>
+      <c r="F54" s="140">
+        <v>13</v>
+      </c>
+      <c r="G54" s="140">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H54" s="140">
+        <f t="shared" si="3"/>
+        <v>46.428571428571431</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="140">
+        <v>1081880</v>
+      </c>
+      <c r="C55" s="140">
+        <v>680</v>
+      </c>
+      <c r="D55" s="140">
+        <v>3</v>
+      </c>
+      <c r="E55" s="140">
+        <v>12</v>
+      </c>
+      <c r="F55" s="140">
+        <v>3</v>
+      </c>
+      <c r="G55" s="140">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H55" s="140">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="140">
+        <v>1120064</v>
+      </c>
+      <c r="C56" s="140">
+        <v>704</v>
+      </c>
+      <c r="D56" s="140">
+        <v>1</v>
+      </c>
+      <c r="E56" s="140">
+        <v>18</v>
+      </c>
+      <c r="F56" s="140">
+        <v>8</v>
+      </c>
+      <c r="G56" s="140">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H56" s="140">
+        <f t="shared" si="3"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="140">
+        <v>1120064</v>
+      </c>
+      <c r="C57" s="140">
+        <v>704</v>
+      </c>
+      <c r="D57" s="140">
+        <v>2</v>
+      </c>
+      <c r="E57" s="140">
+        <v>19</v>
+      </c>
+      <c r="F57" s="140">
+        <v>7</v>
+      </c>
+      <c r="G57" s="140">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="H57" s="140">
+        <f t="shared" si="3"/>
+        <v>36.84210526315789</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="140">
+        <v>1120064</v>
+      </c>
+      <c r="C58" s="140">
+        <v>704</v>
+      </c>
+      <c r="D58" s="140">
+        <v>3</v>
+      </c>
+      <c r="E58" s="140">
+        <v>35</v>
+      </c>
+      <c r="F58" s="140">
+        <v>14</v>
+      </c>
+      <c r="G58" s="140">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="H58" s="140">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="140">
+        <v>3259959</v>
+      </c>
+      <c r="C59" s="140">
+        <v>2049</v>
+      </c>
+      <c r="D59" s="140">
+        <v>1</v>
+      </c>
+      <c r="E59" s="140">
+        <v>16</v>
+      </c>
+      <c r="F59" s="140">
+        <v>6</v>
+      </c>
+      <c r="G59" s="140">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H59" s="140">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" s="140">
+        <v>3259959</v>
+      </c>
+      <c r="C60" s="140">
+        <v>2049</v>
+      </c>
+      <c r="D60" s="140">
+        <v>2</v>
+      </c>
+      <c r="E60" s="140">
+        <v>18</v>
+      </c>
+      <c r="F60" s="140">
+        <v>8</v>
+      </c>
+      <c r="G60" s="140">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H60" s="140">
+        <f t="shared" si="3"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="140">
+        <v>3259959</v>
+      </c>
+      <c r="C61" s="140">
+        <v>2049</v>
+      </c>
+      <c r="D61" s="140">
+        <v>3</v>
+      </c>
+      <c r="E61" s="140">
+        <v>16</v>
+      </c>
+      <c r="F61" s="140">
+        <v>8</v>
+      </c>
+      <c r="G61" s="140">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H61" s="140">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="140">
+        <v>3358601</v>
+      </c>
+      <c r="C62" s="140">
+        <v>2111</v>
+      </c>
+      <c r="D62" s="140">
+        <v>1</v>
+      </c>
+      <c r="E62" s="140">
+        <v>21</v>
+      </c>
+      <c r="F62" s="140">
+        <v>12</v>
+      </c>
+      <c r="G62" s="140">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H62" s="140">
+        <f t="shared" si="3"/>
+        <v>57.142857142857139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="140">
+        <v>3358601</v>
+      </c>
+      <c r="C63" s="140">
+        <v>2111</v>
+      </c>
+      <c r="D63" s="140">
+        <v>2</v>
+      </c>
+      <c r="E63" s="140">
+        <v>18</v>
+      </c>
+      <c r="F63" s="140">
+        <v>8</v>
+      </c>
+      <c r="G63" s="140">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H63" s="140">
+        <f t="shared" si="3"/>
+        <v>44.444444444444443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="140">
+        <v>3358601</v>
+      </c>
+      <c r="C64" s="140">
+        <v>2111</v>
+      </c>
+      <c r="D64" s="140">
+        <v>3</v>
+      </c>
+      <c r="E64" s="140">
+        <v>21</v>
+      </c>
+      <c r="F64" s="140">
+        <v>9</v>
+      </c>
+      <c r="G64" s="140">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="H64" s="140">
+        <f t="shared" si="3"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="140">
+        <v>0</v>
+      </c>
+      <c r="C65" s="140">
+        <v>0</v>
+      </c>
+      <c r="D65" s="140">
+        <v>1</v>
+      </c>
+      <c r="E65" s="140">
+        <v>23</v>
+      </c>
+      <c r="F65" s="140">
+        <v>5</v>
+      </c>
+      <c r="G65" s="140">
+        <f>E65-F65</f>
+        <v>18</v>
+      </c>
+      <c r="H65" s="140">
+        <f>F65/E65*100</f>
+        <v>21.739130434782609</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="140">
+        <v>0</v>
+      </c>
+      <c r="C66" s="140">
+        <v>0</v>
+      </c>
+      <c r="D66" s="140">
+        <v>2</v>
+      </c>
+      <c r="E66" s="140">
+        <v>18</v>
+      </c>
+      <c r="F66" s="140">
+        <v>4</v>
+      </c>
+      <c r="G66" s="140">
+        <f t="shared" ref="G66:G97" si="4">E66-F66</f>
+        <v>14</v>
+      </c>
+      <c r="H66" s="140">
+        <f t="shared" ref="H66:H97" si="5">F66/E66*100</f>
+        <v>22.222222222222221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="140">
+        <v>0</v>
+      </c>
+      <c r="C67" s="140">
+        <v>0</v>
+      </c>
+      <c r="D67" s="140">
+        <v>3</v>
+      </c>
+      <c r="E67" s="140">
+        <v>30</v>
+      </c>
+      <c r="F67" s="140">
+        <v>9</v>
+      </c>
+      <c r="G67" s="140">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="H67" s="140">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" s="140">
+        <v>0</v>
+      </c>
+      <c r="C68" s="140">
+        <v>0</v>
+      </c>
+      <c r="D68" s="140">
+        <v>4</v>
+      </c>
+      <c r="E68" s="140">
+        <v>17</v>
+      </c>
+      <c r="F68" s="140">
+        <v>1</v>
+      </c>
+      <c r="G68" s="140">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="H68" s="140">
+        <f t="shared" si="5"/>
+        <v>5.8823529411764701</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="140">
+        <v>0</v>
+      </c>
+      <c r="C69" s="140">
+        <v>0</v>
+      </c>
+      <c r="D69" s="140">
+        <v>5</v>
+      </c>
+      <c r="E69" s="140">
+        <v>27</v>
+      </c>
+      <c r="F69" s="140">
+        <v>4</v>
+      </c>
+      <c r="G69" s="140">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="H69" s="140">
+        <f t="shared" si="5"/>
+        <v>14.814814814814813</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="140">
+        <v>0</v>
+      </c>
+      <c r="C70" s="140">
+        <v>0</v>
+      </c>
+      <c r="D70" s="140">
+        <v>6</v>
+      </c>
+      <c r="E70" s="140">
+        <v>18</v>
+      </c>
+      <c r="F70" s="140">
+        <v>0</v>
+      </c>
+      <c r="G70" s="140">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H70" s="140">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" s="140">
+        <v>42287</v>
+      </c>
+      <c r="C71" s="140">
+        <v>49</v>
+      </c>
+      <c r="D71" s="140">
+        <v>1</v>
+      </c>
+      <c r="E71" s="140">
+        <v>39</v>
+      </c>
+      <c r="F71" s="140">
+        <v>11</v>
+      </c>
+      <c r="G71" s="140">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="H71" s="140">
+        <f t="shared" si="5"/>
+        <v>28.205128205128204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" s="140">
+        <v>42287</v>
+      </c>
+      <c r="C72" s="140">
+        <v>49</v>
+      </c>
+      <c r="D72" s="140">
+        <v>2</v>
+      </c>
+      <c r="E72" s="140">
+        <v>24</v>
+      </c>
+      <c r="F72" s="140">
+        <v>8</v>
+      </c>
+      <c r="G72" s="140">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="H72" s="140">
+        <f t="shared" si="5"/>
+        <v>33.333333333333329</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" s="140">
+        <v>42287</v>
+      </c>
+      <c r="C73" s="140">
+        <v>49</v>
+      </c>
+      <c r="D73" s="140">
+        <v>3</v>
+      </c>
+      <c r="E73" s="140">
+        <v>20</v>
+      </c>
+      <c r="F73" s="140">
+        <v>6</v>
+      </c>
+      <c r="G73" s="140">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="H73" s="140">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="140">
+        <v>66451</v>
+      </c>
+      <c r="C74" s="140">
+        <v>77</v>
+      </c>
+      <c r="D74" s="140">
+        <v>1</v>
+      </c>
+      <c r="E74" s="140">
+        <v>28</v>
+      </c>
+      <c r="F74" s="140">
+        <v>6</v>
+      </c>
+      <c r="G74" s="140">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H74" s="140">
+        <f t="shared" si="5"/>
+        <v>21.428571428571427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B75" s="140">
+        <v>66451</v>
+      </c>
+      <c r="C75" s="140">
+        <v>77</v>
+      </c>
+      <c r="D75" s="140">
+        <v>2</v>
+      </c>
+      <c r="E75" s="140">
+        <v>20</v>
+      </c>
+      <c r="F75" s="140">
+        <v>2</v>
+      </c>
+      <c r="G75" s="140">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H75" s="140">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="140">
+        <v>66451</v>
+      </c>
+      <c r="C76" s="140">
+        <v>77</v>
+      </c>
+      <c r="D76" s="140">
+        <v>3</v>
+      </c>
+      <c r="E76" s="140">
+        <v>29</v>
+      </c>
+      <c r="F76" s="140">
+        <v>4</v>
+      </c>
+      <c r="G76" s="140">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H76" s="140">
+        <f t="shared" si="5"/>
+        <v>13.793103448275861</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="140">
+        <v>127724</v>
+      </c>
+      <c r="C77" s="140">
+        <v>148</v>
+      </c>
+      <c r="D77" s="140">
+        <v>1</v>
+      </c>
+      <c r="E77" s="140">
+        <v>68</v>
+      </c>
+      <c r="F77" s="140">
+        <v>21</v>
+      </c>
+      <c r="G77" s="140">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="H77" s="140">
+        <f t="shared" si="5"/>
+        <v>30.882352941176471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="140">
+        <v>127724</v>
+      </c>
+      <c r="C78" s="140">
+        <v>148</v>
+      </c>
+      <c r="D78" s="140">
+        <v>2</v>
+      </c>
+      <c r="E78" s="140">
+        <v>41</v>
+      </c>
+      <c r="F78" s="140">
+        <v>12</v>
+      </c>
+      <c r="G78" s="140">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="H78" s="140">
+        <f t="shared" si="5"/>
+        <v>29.268292682926827</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79" s="140">
+        <v>127724</v>
+      </c>
+      <c r="C79" s="140">
+        <v>148</v>
+      </c>
+      <c r="D79" s="140">
+        <v>3</v>
+      </c>
+      <c r="E79" s="140">
+        <v>17</v>
+      </c>
+      <c r="F79" s="140">
+        <v>7</v>
+      </c>
+      <c r="G79" s="140">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H79" s="140">
+        <f t="shared" si="5"/>
+        <v>41.17647058823529</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" s="140">
+        <v>199353</v>
+      </c>
+      <c r="C80" s="140">
+        <v>231</v>
+      </c>
+      <c r="D80" s="140">
+        <v>1</v>
+      </c>
+      <c r="E80" s="140">
+        <v>14</v>
+      </c>
+      <c r="F80" s="140">
+        <v>4</v>
+      </c>
+      <c r="G80" s="140">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H80" s="140">
+        <f t="shared" si="5"/>
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" s="140">
+        <v>199353</v>
+      </c>
+      <c r="C81" s="140">
+        <v>231</v>
+      </c>
+      <c r="D81" s="140">
+        <v>2</v>
+      </c>
+      <c r="E81" s="140">
+        <v>21</v>
+      </c>
+      <c r="F81" s="140">
+        <v>3</v>
+      </c>
+      <c r="G81" s="140">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H81" s="140">
+        <f t="shared" si="5"/>
+        <v>14.285714285714285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" s="140">
+        <v>199353</v>
+      </c>
+      <c r="C82" s="140">
+        <v>231</v>
+      </c>
+      <c r="D82" s="140">
+        <v>3</v>
+      </c>
+      <c r="E82" s="140">
+        <v>39</v>
+      </c>
+      <c r="F82" s="140">
+        <v>5</v>
+      </c>
+      <c r="G82" s="140">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="H82" s="140">
+        <f t="shared" si="5"/>
+        <v>12.820512820512819</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B83" s="140">
+        <v>383172</v>
+      </c>
+      <c r="C83" s="140">
+        <v>444</v>
+      </c>
+      <c r="D83" s="140">
+        <v>1</v>
+      </c>
+      <c r="E83" s="140">
+        <v>82</v>
+      </c>
+      <c r="F83" s="140">
+        <v>24</v>
+      </c>
+      <c r="G83" s="140">
+        <f t="shared" si="4"/>
+        <v>58</v>
+      </c>
+      <c r="H83" s="140">
+        <f t="shared" si="5"/>
+        <v>29.268292682926827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B84" s="140">
+        <v>383172</v>
+      </c>
+      <c r="C84" s="140">
+        <v>444</v>
+      </c>
+      <c r="D84" s="140">
+        <v>2</v>
+      </c>
+      <c r="E84" s="140">
+        <v>25</v>
+      </c>
+      <c r="F84" s="140">
+        <v>8</v>
+      </c>
+      <c r="G84" s="140">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="H84" s="140">
+        <f t="shared" si="5"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B85" s="140">
+        <v>383172</v>
+      </c>
+      <c r="C85" s="140">
+        <v>444</v>
+      </c>
+      <c r="D85" s="140">
+        <v>3</v>
+      </c>
+      <c r="E85" s="140">
+        <v>55</v>
+      </c>
+      <c r="F85" s="140">
+        <v>12</v>
+      </c>
+      <c r="G85" s="140">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="H85" s="140">
+        <f t="shared" si="5"/>
+        <v>21.818181818181817</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" s="140">
+        <v>598922</v>
+      </c>
+      <c r="C86" s="140">
+        <v>694</v>
+      </c>
+      <c r="D86" s="140">
+        <v>1</v>
+      </c>
+      <c r="E86" s="140">
+        <v>17</v>
+      </c>
+      <c r="F86" s="140">
+        <v>5</v>
+      </c>
+      <c r="G86" s="140">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="H86" s="140">
+        <f t="shared" si="5"/>
+        <v>29.411764705882355</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" s="140">
+        <v>598922</v>
+      </c>
+      <c r="C87" s="140">
+        <v>694</v>
+      </c>
+      <c r="D87" s="140">
+        <v>2</v>
+      </c>
+      <c r="E87" s="140">
+        <v>22</v>
+      </c>
+      <c r="F87" s="140">
+        <v>4</v>
+      </c>
+      <c r="G87" s="140">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H87" s="140">
+        <f t="shared" si="5"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B88" s="140">
+        <v>598922</v>
+      </c>
+      <c r="C88" s="140">
+        <v>694</v>
+      </c>
+      <c r="D88" s="140">
+        <v>3</v>
+      </c>
+      <c r="E88" s="140">
+        <v>15</v>
+      </c>
+      <c r="F88" s="140">
+        <v>4</v>
+      </c>
+      <c r="G88" s="140">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="H88" s="140">
+        <f t="shared" si="5"/>
+        <v>26.666666666666668</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="140">
+        <v>1150379</v>
+      </c>
+      <c r="C89" s="140">
+        <v>1333</v>
+      </c>
+      <c r="D89" s="140">
+        <v>1</v>
+      </c>
+      <c r="E89" s="140">
+        <v>21</v>
+      </c>
+      <c r="F89" s="140">
+        <v>8</v>
+      </c>
+      <c r="G89" s="140">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="H89" s="140">
+        <f t="shared" si="5"/>
+        <v>38.095238095238095</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B90" s="140">
+        <v>1150379</v>
+      </c>
+      <c r="C90" s="140">
+        <v>1333</v>
+      </c>
+      <c r="D90" s="140">
+        <v>2</v>
+      </c>
+      <c r="E90" s="140">
+        <v>27</v>
+      </c>
+      <c r="F90" s="140">
+        <v>8</v>
+      </c>
+      <c r="G90" s="140">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="H90" s="140">
+        <f t="shared" si="5"/>
+        <v>29.629629629629626</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B91" s="140">
+        <v>1150379</v>
+      </c>
+      <c r="C91" s="140">
+        <v>1333</v>
+      </c>
+      <c r="D91" s="140">
+        <v>3</v>
+      </c>
+      <c r="E91" s="140">
+        <v>37</v>
+      </c>
+      <c r="F91" s="140">
+        <v>13</v>
+      </c>
+      <c r="G91" s="140">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="H91" s="140">
+        <f t="shared" si="5"/>
+        <v>35.135135135135137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92" s="140">
+        <v>1797629</v>
+      </c>
+      <c r="C92" s="140">
+        <v>2083</v>
+      </c>
+      <c r="D92" s="140">
+        <v>1</v>
+      </c>
+      <c r="E92" s="140">
+        <v>14</v>
+      </c>
+      <c r="F92" s="140">
+        <v>6</v>
+      </c>
+      <c r="G92" s="140">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="H92" s="140">
+        <f t="shared" si="5"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B93" s="140">
+        <v>1797629</v>
+      </c>
+      <c r="C93" s="140">
+        <v>2083</v>
+      </c>
+      <c r="D93" s="140">
+        <v>2</v>
+      </c>
+      <c r="E93" s="140">
+        <v>31</v>
+      </c>
+      <c r="F93" s="140">
+        <v>9</v>
+      </c>
+      <c r="G93" s="140">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H93" s="140">
+        <f t="shared" si="5"/>
+        <v>29.032258064516132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94" s="140">
+        <v>1797629</v>
+      </c>
+      <c r="C94" s="140">
+        <v>2083</v>
+      </c>
+      <c r="D94" s="140">
+        <v>3</v>
+      </c>
+      <c r="E94" s="140">
+        <v>71</v>
+      </c>
+      <c r="F94" s="140">
+        <v>12</v>
+      </c>
+      <c r="G94" s="140">
+        <f t="shared" si="4"/>
+        <v>59</v>
+      </c>
+      <c r="H94" s="140">
+        <f t="shared" si="5"/>
+        <v>16.901408450704224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B95" s="140">
+        <v>3452000</v>
+      </c>
+      <c r="C95" s="140">
+        <v>4000</v>
+      </c>
+      <c r="D95" s="140">
+        <v>1</v>
+      </c>
+      <c r="E95" s="140">
+        <v>19</v>
+      </c>
+      <c r="F95" s="140">
+        <v>8</v>
+      </c>
+      <c r="G95" s="140">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="H95" s="140">
+        <f t="shared" si="5"/>
+        <v>42.105263157894733</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B96" s="140">
+        <v>3452000</v>
+      </c>
+      <c r="C96" s="140">
+        <v>4000</v>
+      </c>
+      <c r="D96" s="140">
+        <v>2</v>
+      </c>
+      <c r="E96" s="140">
+        <v>43</v>
+      </c>
+      <c r="F96" s="140">
+        <v>11</v>
+      </c>
+      <c r="G96" s="140">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="H96" s="140">
+        <f t="shared" si="5"/>
+        <v>25.581395348837212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" s="140">
+        <v>3452000</v>
+      </c>
+      <c r="C97" s="140">
+        <v>4000</v>
+      </c>
+      <c r="D97" s="140">
+        <v>3</v>
+      </c>
+      <c r="E97" s="140">
+        <v>36</v>
+      </c>
+      <c r="F97" s="140">
+        <v>11</v>
+      </c>
+      <c r="G97" s="140">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H97" s="140">
+        <f t="shared" si="5"/>
+        <v>30.555555555555557</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>